--- a/RIDERS/יער קולה XCO גביע מדינה.xlsx
+++ b/RIDERS/יער קולה XCO גביע מדינה.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\.shortcut-targets-by-id\1V13-ga8yDzCABIlXk3aGqKAQxXDU9CUi\מחלקת שיפוט ומדידה איגוד האופניים\ציקי\2021-2022\תחרויות\4אפריל 22\קולה בינלאומי גביע 1.4.2022\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev2026\commissaire\RIDERS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8BC8070-C919-4786-B091-02C5EFC334E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17148" yWindow="-14340" windowWidth="16752" windowHeight="9732" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="דירוג לזינוק" sheetId="1" r:id="rId1"/>
@@ -4039,7 +4039,7 @@
       <b/>
       <sz val="14"/>
       <color theme="5" tint="-0.249977111117893"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4047,7 +4047,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4068,7 +4068,7 @@
       <b/>
       <sz val="12"/>
       <color theme="5" tint="-0.249977111117893"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4096,7 +4096,7 @@
       <b/>
       <sz val="14"/>
       <color theme="5" tint="-0.249977111117893"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -4112,7 +4112,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
@@ -4568,30 +4568,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="430">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="424">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4609,105 +4609,105 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4719,10 +4719,10 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4732,36 +4732,36 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4770,7 +4770,7 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4794,13 +4794,13 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4845,13 +4845,13 @@
     <xf numFmtId="20" fontId="13" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="13" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4875,10 +4875,10 @@
     <xf numFmtId="20" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4888,10 +4888,10 @@
     <xf numFmtId="20" fontId="13" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4901,10 +4901,10 @@
     <xf numFmtId="20" fontId="13" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4914,10 +4914,10 @@
     <xf numFmtId="20" fontId="13" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4930,10 +4930,10 @@
     <xf numFmtId="20" fontId="13" fillId="7" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4943,10 +4943,10 @@
     <xf numFmtId="20" fontId="13" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4956,10 +4956,10 @@
     <xf numFmtId="20" fontId="13" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4969,10 +4969,10 @@
     <xf numFmtId="20" fontId="13" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4985,7 +4985,7 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5030,16 +5030,16 @@
     <xf numFmtId="0" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5111,21 +5111,21 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5155,10 +5155,10 @@
     <xf numFmtId="0" fontId="15" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5171,10 +5171,10 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5196,10 +5196,10 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5212,10 +5212,10 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5228,10 +5228,10 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5244,10 +5244,10 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5260,10 +5260,10 @@
     <xf numFmtId="0" fontId="17" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5276,10 +5276,10 @@
     <xf numFmtId="0" fontId="17" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5298,10 +5298,10 @@
     <xf numFmtId="0" fontId="15" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5311,10 +5311,10 @@
     <xf numFmtId="0" fontId="17" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5327,10 +5327,10 @@
     <xf numFmtId="0" fontId="15" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5343,208 +5343,199 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="12" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="12" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="11" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="10" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5571,14 +5562,14 @@
     <xf numFmtId="0" fontId="17" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5593,14 +5584,14 @@
     <xf numFmtId="0" fontId="17" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="13" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5615,14 +5606,14 @@
     <xf numFmtId="0" fontId="17" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5637,14 +5628,14 @@
     <xf numFmtId="0" fontId="17" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="13" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5675,12 +5666,11 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5689,7 +5679,7 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5698,7 +5688,7 @@
     <xf numFmtId="20" fontId="13" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5716,14 +5706,8 @@
     <xf numFmtId="20" fontId="14" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5734,14 +5718,14 @@
     <xf numFmtId="0" fontId="15" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="14" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5756,7 +5740,7 @@
     <xf numFmtId="0" fontId="20" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5789,7 +5773,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="הרים - גביע המדינה XCO"/>
@@ -38905,9 +38889,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -38945,7 +38929,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -39051,7 +39035,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -39193,7 +39177,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -39222,7 +39206,7 @@
     <col min="16" max="16" width="10.109375" style="81" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="36.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="157" t="s">
         <v>1284</v>
       </c>
@@ -39253,7 +39237,7 @@
       <c r="J1" s="4" t="s">
         <v>1293</v>
       </c>
-      <c r="K1" s="326" t="s">
+      <c r="K1" s="324" t="s">
         <v>1294</v>
       </c>
       <c r="L1" s="285" t="s">
@@ -39262,7 +39246,7 @@
       <c r="M1" s="285" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="359" t="s">
+      <c r="N1" s="356" t="s">
         <v>1285</v>
       </c>
       <c r="O1" s="285" t="s">
@@ -39777,7 +39761,7 @@
       <c r="D12" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="288">
+      <c r="E12" s="52">
         <v>39335047</v>
       </c>
       <c r="F12" s="51" t="s">
@@ -39825,7 +39809,7 @@
       <c r="D13" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="288">
+      <c r="E13" s="52">
         <v>36101145</v>
       </c>
       <c r="F13" s="51" t="s">
@@ -39873,7 +39857,7 @@
       <c r="D14" s="51" t="s">
         <v>153</v>
       </c>
-      <c r="E14" s="288">
+      <c r="E14" s="52">
         <v>34694570</v>
       </c>
       <c r="F14" s="51" t="s">
@@ -39921,7 +39905,7 @@
       <c r="D15" s="51" t="s">
         <v>1202</v>
       </c>
-      <c r="E15" s="288">
+      <c r="E15" s="52">
         <v>32557001</v>
       </c>
       <c r="F15" s="51" t="s">
@@ -39969,7 +39953,7 @@
       <c r="D16" s="51" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="288">
+      <c r="E16" s="52">
         <v>36795359</v>
       </c>
       <c r="F16" s="51" t="s">
@@ -40017,7 +40001,7 @@
       <c r="D17" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="288">
+      <c r="E17" s="52">
         <v>17033481</v>
       </c>
       <c r="F17" s="51" t="s">
@@ -40065,7 +40049,7 @@
       <c r="D18" s="76" t="s">
         <v>153</v>
       </c>
-      <c r="E18" s="289">
+      <c r="E18" s="78">
         <v>37201829</v>
       </c>
       <c r="F18" s="76" t="s">
@@ -40083,7 +40067,7 @@
       <c r="J18" s="76" t="s">
         <v>236</v>
       </c>
-      <c r="K18" s="409">
+      <c r="K18" s="405">
         <v>10002474490</v>
       </c>
       <c r="L18" s="78" t="s">
@@ -40103,7 +40087,7 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="410">
+      <c r="A19" s="406">
         <v>1</v>
       </c>
       <c r="B19" s="222" t="s">
@@ -40115,7 +40099,7 @@
       <c r="D19" s="223" t="s">
         <v>407</v>
       </c>
-      <c r="E19" s="315">
+      <c r="E19" s="313">
         <v>215125139</v>
       </c>
       <c r="F19" s="223" t="s">
@@ -40133,8 +40117,8 @@
       <c r="J19" s="223" t="s">
         <v>740</v>
       </c>
-      <c r="K19" s="337"/>
-      <c r="L19" s="337" t="s">
+      <c r="K19" s="334"/>
+      <c r="L19" s="334" t="s">
         <v>741</v>
       </c>
       <c r="M19" s="224" t="s">
@@ -40143,10 +40127,10 @@
       <c r="N19" s="225">
         <v>104</v>
       </c>
-      <c r="O19" s="411" t="s">
+      <c r="O19" s="407" t="s">
         <v>1306</v>
       </c>
-      <c r="P19" s="412">
+      <c r="P19" s="408">
         <v>0.35416666666666669</v>
       </c>
     </row>
@@ -40163,7 +40147,7 @@
       <c r="D20" s="122" t="s">
         <v>500</v>
       </c>
-      <c r="E20" s="302">
+      <c r="E20" s="300">
         <v>323768481</v>
       </c>
       <c r="F20" s="122" t="s">
@@ -40181,8 +40165,8 @@
       <c r="J20" s="122" t="s">
         <v>504</v>
       </c>
-      <c r="K20" s="338"/>
-      <c r="L20" s="338" t="s">
+      <c r="K20" s="335"/>
+      <c r="L20" s="335" t="s">
         <v>505</v>
       </c>
       <c r="M20" s="123" t="s">
@@ -40191,10 +40175,10 @@
       <c r="N20" s="124">
         <v>106</v>
       </c>
-      <c r="O20" s="413" t="s">
+      <c r="O20" s="409" t="s">
         <v>1306</v>
       </c>
-      <c r="P20" s="414">
+      <c r="P20" s="410">
         <v>0.35416666666666669</v>
       </c>
     </row>
@@ -40211,7 +40195,7 @@
       <c r="D21" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="E21" s="302">
+      <c r="E21" s="300">
         <v>327731881</v>
       </c>
       <c r="F21" s="122" t="s">
@@ -40229,8 +40213,8 @@
       <c r="J21" s="122" t="s">
         <v>512</v>
       </c>
-      <c r="K21" s="338"/>
-      <c r="L21" s="338" t="s">
+      <c r="K21" s="335"/>
+      <c r="L21" s="335" t="s">
         <v>1073</v>
       </c>
       <c r="M21" s="123" t="s">
@@ -40239,10 +40223,10 @@
       <c r="N21" s="124">
         <v>113</v>
       </c>
-      <c r="O21" s="413" t="s">
+      <c r="O21" s="409" t="s">
         <v>1306</v>
       </c>
-      <c r="P21" s="414">
+      <c r="P21" s="410">
         <v>0.35416666666666669</v>
       </c>
     </row>
@@ -40259,7 +40243,7 @@
       <c r="D22" s="122" t="s">
         <v>153</v>
       </c>
-      <c r="E22" s="415">
+      <c r="E22" s="335">
         <v>60142502</v>
       </c>
       <c r="F22" s="122" t="s">
@@ -40277,8 +40261,8 @@
       <c r="J22" s="122" t="s">
         <v>536</v>
       </c>
-      <c r="K22" s="338"/>
-      <c r="L22" s="338" t="s">
+      <c r="K22" s="335"/>
+      <c r="L22" s="335" t="s">
         <v>537</v>
       </c>
       <c r="M22" s="123" t="s">
@@ -40287,10 +40271,10 @@
       <c r="N22" s="124">
         <v>114</v>
       </c>
-      <c r="O22" s="413" t="s">
+      <c r="O22" s="409" t="s">
         <v>1306</v>
       </c>
-      <c r="P22" s="414">
+      <c r="P22" s="410">
         <v>0.35416666666666669</v>
       </c>
     </row>
@@ -40307,7 +40291,7 @@
       <c r="D23" s="122" t="s">
         <v>153</v>
       </c>
-      <c r="E23" s="415">
+      <c r="E23" s="335">
         <v>24963241</v>
       </c>
       <c r="F23" s="122" t="s">
@@ -40325,8 +40309,8 @@
       <c r="J23" s="122" t="s">
         <v>508</v>
       </c>
-      <c r="K23" s="338"/>
-      <c r="L23" s="338" t="s">
+      <c r="K23" s="335"/>
+      <c r="L23" s="335" t="s">
         <v>509</v>
       </c>
       <c r="M23" s="123" t="s">
@@ -40335,10 +40319,10 @@
       <c r="N23" s="124">
         <v>115</v>
       </c>
-      <c r="O23" s="413" t="s">
+      <c r="O23" s="409" t="s">
         <v>1306</v>
       </c>
-      <c r="P23" s="414">
+      <c r="P23" s="410">
         <v>0.35416666666666669</v>
       </c>
     </row>
@@ -40355,7 +40339,7 @@
       <c r="D24" s="122" t="s">
         <v>376</v>
       </c>
-      <c r="E24" s="415">
+      <c r="E24" s="335">
         <v>23832447</v>
       </c>
       <c r="F24" s="122" t="s">
@@ -40373,10 +40357,10 @@
       <c r="J24" s="122" t="s">
         <v>987</v>
       </c>
-      <c r="K24" s="302">
+      <c r="K24" s="300">
         <v>10119675651</v>
       </c>
-      <c r="L24" s="338" t="s">
+      <c r="L24" s="335" t="s">
         <v>988</v>
       </c>
       <c r="M24" s="123" t="s">
@@ -40385,10 +40369,10 @@
       <c r="N24" s="124">
         <v>118</v>
       </c>
-      <c r="O24" s="413" t="s">
+      <c r="O24" s="409" t="s">
         <v>1306</v>
       </c>
-      <c r="P24" s="414">
+      <c r="P24" s="410">
         <v>0.35416666666666669</v>
       </c>
     </row>
@@ -40405,7 +40389,7 @@
       <c r="D25" s="122" t="s">
         <v>407</v>
       </c>
-      <c r="E25" s="302">
+      <c r="E25" s="300">
         <v>212835516</v>
       </c>
       <c r="F25" s="122" t="s">
@@ -40423,8 +40407,8 @@
       <c r="J25" s="122" t="s">
         <v>1238</v>
       </c>
-      <c r="K25" s="338"/>
-      <c r="L25" s="338" t="s">
+      <c r="K25" s="335"/>
+      <c r="L25" s="335" t="s">
         <v>1239</v>
       </c>
       <c r="M25" s="123" t="s">
@@ -40433,15 +40417,15 @@
       <c r="N25" s="124">
         <v>124</v>
       </c>
-      <c r="O25" s="413" t="s">
+      <c r="O25" s="409" t="s">
         <v>1306</v>
       </c>
-      <c r="P25" s="414">
+      <c r="P25" s="410">
         <v>0.35416666666666669</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="416">
+      <c r="A26" s="411">
         <v>8</v>
       </c>
       <c r="B26" s="126" t="s">
@@ -40453,7 +40437,7 @@
       <c r="D26" s="127" t="s">
         <v>190</v>
       </c>
-      <c r="E26" s="417">
+      <c r="E26" s="336">
         <v>34367920</v>
       </c>
       <c r="F26" s="127" t="s">
@@ -40471,8 +40455,8 @@
       <c r="J26" s="127" t="s">
         <v>851</v>
       </c>
-      <c r="K26" s="339"/>
-      <c r="L26" s="339" t="s">
+      <c r="K26" s="336"/>
+      <c r="L26" s="336" t="s">
         <v>852</v>
       </c>
       <c r="M26" s="128" t="s">
@@ -40481,10 +40465,10 @@
       <c r="N26" s="129">
         <v>125</v>
       </c>
-      <c r="O26" s="418" t="s">
+      <c r="O26" s="412" t="s">
         <v>1306</v>
       </c>
-      <c r="P26" s="419">
+      <c r="P26" s="413">
         <v>0.35416666666666669</v>
       </c>
     </row>
@@ -40502,7 +40486,7 @@
       <c r="D27" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="E27" s="290">
+      <c r="E27" s="288">
         <v>66425661</v>
       </c>
       <c r="F27" s="61" t="s">
@@ -40520,8 +40504,8 @@
       <c r="J27" s="61" t="s">
         <v>1245</v>
       </c>
-      <c r="K27" s="327"/>
-      <c r="L27" s="327" t="s">
+      <c r="K27" s="288"/>
+      <c r="L27" s="288" t="s">
         <v>1246</v>
       </c>
       <c r="M27" s="62" t="s">
@@ -40537,7 +40521,7 @@
         <v>0.35416666666666669</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" ht="36.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A28" s="157" t="s">
         <v>1284</v>
       </c>
@@ -40568,7 +40552,7 @@
       <c r="J28" s="4" t="s">
         <v>1293</v>
       </c>
-      <c r="K28" s="326" t="s">
+      <c r="K28" s="324" t="s">
         <v>1294</v>
       </c>
       <c r="L28" s="285" t="s">
@@ -40577,7 +40561,7 @@
       <c r="M28" s="285" t="s">
         <v>5</v>
       </c>
-      <c r="N28" s="359" t="s">
+      <c r="N28" s="356" t="s">
         <v>1285</v>
       </c>
       <c r="O28" s="285" t="s">
@@ -40600,7 +40584,7 @@
       <c r="D29" s="73" t="s">
         <v>519</v>
       </c>
-      <c r="E29" s="291">
+      <c r="E29" s="289">
         <v>329557227</v>
       </c>
       <c r="F29" s="73" t="s">
@@ -40618,8 +40602,8 @@
       <c r="J29" s="73" t="s">
         <v>944</v>
       </c>
-      <c r="K29" s="328"/>
-      <c r="L29" s="328" t="s">
+      <c r="K29" s="325"/>
+      <c r="L29" s="325" t="s">
         <v>945</v>
       </c>
       <c r="M29" s="64" t="s">
@@ -40648,7 +40632,7 @@
       <c r="D30" s="66" t="s">
         <v>407</v>
       </c>
-      <c r="E30" s="292">
+      <c r="E30" s="290">
         <v>215619701</v>
       </c>
       <c r="F30" s="66" t="s">
@@ -40666,10 +40650,10 @@
       <c r="J30" s="66" t="s">
         <v>1151</v>
       </c>
-      <c r="K30" s="292">
+      <c r="K30" s="290">
         <v>10100358709</v>
       </c>
-      <c r="L30" s="329" t="s">
+      <c r="L30" s="326" t="s">
         <v>1152</v>
       </c>
       <c r="M30" s="67" t="s">
@@ -40698,7 +40682,7 @@
       <c r="D31" s="66" t="s">
         <v>519</v>
       </c>
-      <c r="E31" s="292">
+      <c r="E31" s="290">
         <v>216069310</v>
       </c>
       <c r="F31" s="66" t="s">
@@ -40716,10 +40700,10 @@
       <c r="J31" s="66" t="s">
         <v>521</v>
       </c>
-      <c r="K31" s="292">
+      <c r="K31" s="290">
         <v>10119675045</v>
       </c>
-      <c r="L31" s="329" t="s">
+      <c r="L31" s="326" t="s">
         <v>522</v>
       </c>
       <c r="M31" s="67" t="s">
@@ -40748,7 +40732,7 @@
       <c r="D32" s="66" t="s">
         <v>376</v>
       </c>
-      <c r="E32" s="292">
+      <c r="E32" s="290">
         <v>327945499</v>
       </c>
       <c r="F32" s="66" t="s">
@@ -40766,10 +40750,10 @@
       <c r="J32" s="66" t="s">
         <v>987</v>
       </c>
-      <c r="K32" s="292">
+      <c r="K32" s="290">
         <v>10119675550</v>
       </c>
-      <c r="L32" s="329" t="s">
+      <c r="L32" s="326" t="s">
         <v>996</v>
       </c>
       <c r="M32" s="67" t="s">
@@ -40798,7 +40782,7 @@
       <c r="D33" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="E33" s="292">
+      <c r="E33" s="290">
         <v>326775731</v>
       </c>
       <c r="F33" s="66" t="s">
@@ -40816,8 +40800,8 @@
       <c r="J33" s="66" t="s">
         <v>941</v>
       </c>
-      <c r="K33" s="329"/>
-      <c r="L33" s="329" t="s">
+      <c r="K33" s="326"/>
+      <c r="L33" s="326" t="s">
         <v>942</v>
       </c>
       <c r="M33" s="67" t="s">
@@ -40846,7 +40830,7 @@
       <c r="D34" s="66" t="s">
         <v>190</v>
       </c>
-      <c r="E34" s="292">
+      <c r="E34" s="290">
         <v>329131247</v>
       </c>
       <c r="F34" s="66" t="s">
@@ -40864,8 +40848,8 @@
       <c r="J34" s="66" t="s">
         <v>1119</v>
       </c>
-      <c r="K34" s="329"/>
-      <c r="L34" s="329" t="s">
+      <c r="K34" s="326"/>
+      <c r="L34" s="326" t="s">
         <v>1120</v>
       </c>
       <c r="M34" s="67" t="s">
@@ -40894,7 +40878,7 @@
       <c r="D35" s="66" t="s">
         <v>407</v>
       </c>
-      <c r="E35" s="292">
+      <c r="E35" s="290">
         <v>328339478</v>
       </c>
       <c r="F35" s="66" t="s">
@@ -40912,10 +40896,10 @@
       <c r="J35" s="66" t="s">
         <v>836</v>
       </c>
-      <c r="K35" s="292">
+      <c r="K35" s="290">
         <v>10127763734</v>
       </c>
-      <c r="L35" s="329" t="s">
+      <c r="L35" s="326" t="s">
         <v>837</v>
       </c>
       <c r="M35" s="67" t="s">
@@ -40944,7 +40928,7 @@
       <c r="D36" s="66" t="s">
         <v>376</v>
       </c>
-      <c r="E36" s="292">
+      <c r="E36" s="290">
         <v>326769783</v>
       </c>
       <c r="F36" s="66" t="s">
@@ -40962,10 +40946,10 @@
       <c r="J36" s="66" t="s">
         <v>1003</v>
       </c>
-      <c r="K36" s="292">
+      <c r="K36" s="290">
         <v>10118080508</v>
       </c>
-      <c r="L36" s="329" t="s">
+      <c r="L36" s="326" t="s">
         <v>1004</v>
       </c>
       <c r="M36" s="67" t="s">
@@ -40994,7 +40978,7 @@
       <c r="D37" s="66" t="s">
         <v>965</v>
       </c>
-      <c r="E37" s="292">
+      <c r="E37" s="290">
         <v>217297225</v>
       </c>
       <c r="F37" s="66" t="s">
@@ -41012,8 +40996,8 @@
       <c r="J37" s="66" t="s">
         <v>1164</v>
       </c>
-      <c r="K37" s="329"/>
-      <c r="L37" s="329" t="s">
+      <c r="K37" s="326"/>
+      <c r="L37" s="326" t="s">
         <v>1165</v>
       </c>
       <c r="M37" s="67" t="s">
@@ -41042,7 +41026,7 @@
       <c r="D38" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="293">
+      <c r="E38" s="291">
         <v>330878844</v>
       </c>
       <c r="F38" s="74" t="s">
@@ -41090,7 +41074,7 @@
       <c r="D39" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="E39" s="292">
+      <c r="E39" s="290">
         <v>215472408</v>
       </c>
       <c r="F39" s="66" t="s">
@@ -41108,8 +41092,8 @@
       <c r="J39" s="66" t="s">
         <v>1217</v>
       </c>
-      <c r="K39" s="329"/>
-      <c r="L39" s="329" t="s">
+      <c r="K39" s="326"/>
+      <c r="L39" s="326" t="s">
         <v>1218</v>
       </c>
       <c r="M39" s="67" t="s">
@@ -41138,7 +41122,7 @@
       <c r="D40" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="E40" s="292">
+      <c r="E40" s="290">
         <v>215759606</v>
       </c>
       <c r="F40" s="66" t="s">
@@ -41156,8 +41140,8 @@
       <c r="J40" s="66" t="s">
         <v>974</v>
       </c>
-      <c r="K40" s="329"/>
-      <c r="L40" s="329" t="s">
+      <c r="K40" s="326"/>
+      <c r="L40" s="326" t="s">
         <v>975</v>
       </c>
       <c r="M40" s="67" t="s">
@@ -41186,7 +41170,7 @@
       <c r="D41" s="66" t="s">
         <v>333</v>
       </c>
-      <c r="E41" s="292">
+      <c r="E41" s="290">
         <v>216587501</v>
       </c>
       <c r="F41" s="66" t="s">
@@ -41204,8 +41188,8 @@
       <c r="J41" s="66" t="s">
         <v>823</v>
       </c>
-      <c r="K41" s="329"/>
-      <c r="L41" s="329" t="s">
+      <c r="K41" s="326"/>
+      <c r="L41" s="326" t="s">
         <v>824</v>
       </c>
       <c r="M41" s="67" t="s">
@@ -41234,7 +41218,7 @@
       <c r="D42" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="E42" s="292">
+      <c r="E42" s="290">
         <v>330577750</v>
       </c>
       <c r="F42" s="66" t="s">
@@ -41252,8 +41236,8 @@
       <c r="J42" s="66" t="s">
         <v>1097</v>
       </c>
-      <c r="K42" s="329"/>
-      <c r="L42" s="329" t="s">
+      <c r="K42" s="326"/>
+      <c r="L42" s="326" t="s">
         <v>1098</v>
       </c>
       <c r="M42" s="67" t="s">
@@ -41282,7 +41266,7 @@
       <c r="D43" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="E43" s="292">
+      <c r="E43" s="290">
         <v>216787259</v>
       </c>
       <c r="F43" s="66" t="s">
@@ -41300,8 +41284,8 @@
       <c r="J43" s="66" t="s">
         <v>290</v>
       </c>
-      <c r="K43" s="329"/>
-      <c r="L43" s="329" t="s">
+      <c r="K43" s="326"/>
+      <c r="L43" s="326" t="s">
         <v>291</v>
       </c>
       <c r="M43" s="67" t="s">
@@ -41330,7 +41314,7 @@
       <c r="D44" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="E44" s="292">
+      <c r="E44" s="290">
         <v>329157986</v>
       </c>
       <c r="F44" s="66" t="s">
@@ -41348,8 +41332,8 @@
       <c r="J44" s="66" t="s">
         <v>1149</v>
       </c>
-      <c r="K44" s="329"/>
-      <c r="L44" s="329" t="s">
+      <c r="K44" s="326"/>
+      <c r="L44" s="326" t="s">
         <v>1150</v>
       </c>
       <c r="M44" s="67" t="s">
@@ -41378,7 +41362,7 @@
       <c r="D45" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="E45" s="292">
+      <c r="E45" s="290">
         <v>330575564</v>
       </c>
       <c r="F45" s="66" t="s">
@@ -41396,8 +41380,8 @@
       <c r="J45" s="66" t="s">
         <v>959</v>
       </c>
-      <c r="K45" s="329"/>
-      <c r="L45" s="329" t="s">
+      <c r="K45" s="326"/>
+      <c r="L45" s="326" t="s">
         <v>960</v>
       </c>
       <c r="M45" s="67" t="s">
@@ -41426,7 +41410,7 @@
       <c r="D46" s="66" t="s">
         <v>510</v>
       </c>
-      <c r="E46" s="292">
+      <c r="E46" s="290">
         <v>216215046</v>
       </c>
       <c r="F46" s="66" t="s">
@@ -41444,10 +41428,10 @@
       <c r="J46" s="66" t="s">
         <v>388</v>
       </c>
-      <c r="K46" s="292">
+      <c r="K46" s="290">
         <v>10118783352</v>
       </c>
-      <c r="L46" s="329" t="s">
+      <c r="L46" s="326" t="s">
         <v>1009</v>
       </c>
       <c r="M46" s="67" t="s">
@@ -41476,7 +41460,7 @@
       <c r="D47" s="66" t="s">
         <v>370</v>
       </c>
-      <c r="E47" s="292">
+      <c r="E47" s="290">
         <v>340903525</v>
       </c>
       <c r="F47" s="66" t="s">
@@ -41494,10 +41478,10 @@
       <c r="J47" s="66" t="s">
         <v>374</v>
       </c>
-      <c r="K47" s="292">
+      <c r="K47" s="290">
         <v>10119675449</v>
       </c>
-      <c r="L47" s="329" t="s">
+      <c r="L47" s="326" t="s">
         <v>375</v>
       </c>
       <c r="M47" s="67" t="s">
@@ -41526,7 +41510,7 @@
       <c r="D48" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="E48" s="292">
+      <c r="E48" s="290">
         <v>329608681</v>
       </c>
       <c r="F48" s="66" t="s">
@@ -41544,8 +41528,8 @@
       <c r="J48" s="66" t="s">
         <v>305</v>
       </c>
-      <c r="K48" s="329"/>
-      <c r="L48" s="329" t="s">
+      <c r="K48" s="326"/>
+      <c r="L48" s="326" t="s">
         <v>306</v>
       </c>
       <c r="M48" s="67" t="s">
@@ -41574,7 +41558,7 @@
       <c r="D49" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="E49" s="292">
+      <c r="E49" s="290">
         <v>216060913</v>
       </c>
       <c r="F49" s="66" t="s">
@@ -41592,8 +41576,8 @@
       <c r="J49" s="66" t="s">
         <v>548</v>
       </c>
-      <c r="K49" s="329"/>
-      <c r="L49" s="329" t="s">
+      <c r="K49" s="326"/>
+      <c r="L49" s="326" t="s">
         <v>549</v>
       </c>
       <c r="M49" s="67" t="s">
@@ -41622,7 +41606,7 @@
       <c r="D50" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="E50" s="292">
+      <c r="E50" s="290">
         <v>216027383</v>
       </c>
       <c r="F50" s="66" t="s">
@@ -41640,8 +41624,8 @@
       <c r="J50" s="66" t="s">
         <v>1229</v>
       </c>
-      <c r="K50" s="329"/>
-      <c r="L50" s="329" t="s">
+      <c r="K50" s="326"/>
+      <c r="L50" s="326" t="s">
         <v>1230</v>
       </c>
       <c r="M50" s="67" t="s">
@@ -41670,7 +41654,7 @@
       <c r="D51" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="E51" s="292">
+      <c r="E51" s="290">
         <v>216173070</v>
       </c>
       <c r="F51" s="66" t="s">
@@ -41688,8 +41672,8 @@
       <c r="J51" s="66" t="s">
         <v>949</v>
       </c>
-      <c r="K51" s="329"/>
-      <c r="L51" s="329" t="s">
+      <c r="K51" s="326"/>
+      <c r="L51" s="326" t="s">
         <v>950</v>
       </c>
       <c r="M51" s="67" t="s">
@@ -41718,7 +41702,7 @@
       <c r="D52" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="292">
+      <c r="E52" s="290">
         <v>217328004</v>
       </c>
       <c r="F52" s="66" t="s">
@@ -41736,8 +41720,8 @@
       <c r="J52" s="66" t="s">
         <v>1169</v>
       </c>
-      <c r="K52" s="329"/>
-      <c r="L52" s="329" t="s">
+      <c r="K52" s="326"/>
+      <c r="L52" s="326" t="s">
         <v>1170</v>
       </c>
       <c r="M52" s="67" t="s">
@@ -41766,7 +41750,7 @@
       <c r="D53" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="E53" s="292">
+      <c r="E53" s="290">
         <v>217224336</v>
       </c>
       <c r="F53" s="66" t="s">
@@ -41784,8 +41768,8 @@
       <c r="J53" s="66" t="s">
         <v>1006</v>
       </c>
-      <c r="K53" s="329"/>
-      <c r="L53" s="329" t="s">
+      <c r="K53" s="326"/>
+      <c r="L53" s="326" t="s">
         <v>1007</v>
       </c>
       <c r="M53" s="67" t="s">
@@ -41814,7 +41798,7 @@
       <c r="D54" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="E54" s="292">
+      <c r="E54" s="290">
         <v>216342832</v>
       </c>
       <c r="F54" s="66" t="s">
@@ -41832,8 +41816,8 @@
       <c r="J54" s="66" t="s">
         <v>355</v>
       </c>
-      <c r="K54" s="329"/>
-      <c r="L54" s="329" t="s">
+      <c r="K54" s="326"/>
+      <c r="L54" s="326" t="s">
         <v>356</v>
       </c>
       <c r="M54" s="67" t="s">
@@ -41862,7 +41846,7 @@
       <c r="D55" s="66" t="s">
         <v>376</v>
       </c>
-      <c r="E55" s="292">
+      <c r="E55" s="290">
         <v>328384359</v>
       </c>
       <c r="F55" s="66" t="s">
@@ -41880,8 +41864,8 @@
       <c r="J55" s="66" t="s">
         <v>1156</v>
       </c>
-      <c r="K55" s="329"/>
-      <c r="L55" s="329" t="s">
+      <c r="K55" s="326"/>
+      <c r="L55" s="326" t="s">
         <v>1157</v>
       </c>
       <c r="M55" s="67" t="s">
@@ -41910,7 +41894,7 @@
       <c r="D56" s="66" t="s">
         <v>376</v>
       </c>
-      <c r="E56" s="292">
+      <c r="E56" s="290">
         <v>215933391</v>
       </c>
       <c r="F56" s="66" t="s">
@@ -41928,8 +41912,8 @@
       <c r="J56" s="66" t="s">
         <v>999</v>
       </c>
-      <c r="K56" s="329"/>
-      <c r="L56" s="329" t="s">
+      <c r="K56" s="326"/>
+      <c r="L56" s="326" t="s">
         <v>1000</v>
       </c>
       <c r="M56" s="67" t="s">
@@ -41958,7 +41942,7 @@
       <c r="D57" s="66" t="s">
         <v>407</v>
       </c>
-      <c r="E57" s="292">
+      <c r="E57" s="290">
         <v>331718056</v>
       </c>
       <c r="F57" s="66" t="s">
@@ -41976,8 +41960,8 @@
       <c r="J57" s="66" t="s">
         <v>751</v>
       </c>
-      <c r="K57" s="329"/>
-      <c r="L57" s="329" t="s">
+      <c r="K57" s="326"/>
+      <c r="L57" s="326" t="s">
         <v>752</v>
       </c>
       <c r="M57" s="67" t="s">
@@ -42006,7 +41990,7 @@
       <c r="D58" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="E58" s="292">
+      <c r="E58" s="290">
         <v>328316930</v>
       </c>
       <c r="F58" s="66" t="s">
@@ -42024,8 +42008,8 @@
       <c r="J58" s="66" t="s">
         <v>930</v>
       </c>
-      <c r="K58" s="329"/>
-      <c r="L58" s="329" t="s">
+      <c r="K58" s="326"/>
+      <c r="L58" s="326" t="s">
         <v>931</v>
       </c>
       <c r="M58" s="67" t="s">
@@ -42054,7 +42038,7 @@
       <c r="D59" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="E59" s="292">
+      <c r="E59" s="290">
         <v>329469340</v>
       </c>
       <c r="F59" s="66" t="s">
@@ -42072,8 +42056,8 @@
       <c r="J59" s="66" t="s">
         <v>219</v>
       </c>
-      <c r="K59" s="329"/>
-      <c r="L59" s="329" t="s">
+      <c r="K59" s="326"/>
+      <c r="L59" s="326" t="s">
         <v>220</v>
       </c>
       <c r="M59" s="67" t="s">
@@ -42102,7 +42086,7 @@
       <c r="D60" s="66" t="s">
         <v>376</v>
       </c>
-      <c r="E60" s="292">
+      <c r="E60" s="290">
         <v>216651927</v>
       </c>
       <c r="F60" s="66" t="s">
@@ -42120,8 +42104,8 @@
       <c r="J60" s="66" t="s">
         <v>512</v>
       </c>
-      <c r="K60" s="329"/>
-      <c r="L60" s="329" t="s">
+      <c r="K60" s="326"/>
+      <c r="L60" s="326" t="s">
         <v>964</v>
       </c>
       <c r="M60" s="67" t="s">
@@ -42150,7 +42134,7 @@
       <c r="D61" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="E61" s="292">
+      <c r="E61" s="290">
         <v>216326991</v>
       </c>
       <c r="F61" s="66" t="s">
@@ -42168,8 +42152,8 @@
       <c r="J61" s="66" t="s">
         <v>672</v>
       </c>
-      <c r="K61" s="329"/>
-      <c r="L61" s="329" t="s">
+      <c r="K61" s="326"/>
+      <c r="L61" s="326" t="s">
         <v>673</v>
       </c>
       <c r="M61" s="67" t="s">
@@ -42198,7 +42182,7 @@
       <c r="D62" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="E62" s="292">
+      <c r="E62" s="290">
         <v>330594896</v>
       </c>
       <c r="F62" s="66" t="s">
@@ -42216,8 +42200,8 @@
       <c r="J62" s="66" t="s">
         <v>166</v>
       </c>
-      <c r="K62" s="329"/>
-      <c r="L62" s="329" t="s">
+      <c r="K62" s="326"/>
+      <c r="L62" s="326" t="s">
         <v>167</v>
       </c>
       <c r="M62" s="67" t="s">
@@ -42246,7 +42230,7 @@
       <c r="D63" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="E63" s="292">
+      <c r="E63" s="290">
         <v>328362470</v>
       </c>
       <c r="F63" s="66" t="s">
@@ -42264,8 +42248,8 @@
       <c r="J63" s="66" t="s">
         <v>1220</v>
       </c>
-      <c r="K63" s="329"/>
-      <c r="L63" s="329" t="s">
+      <c r="K63" s="326"/>
+      <c r="L63" s="326" t="s">
         <v>1221</v>
       </c>
       <c r="M63" s="67" t="s">
@@ -42294,7 +42278,7 @@
       <c r="D64" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="E64" s="292">
+      <c r="E64" s="290">
         <v>327619573</v>
       </c>
       <c r="F64" s="66" t="s">
@@ -42312,8 +42296,8 @@
       <c r="J64" s="66" t="s">
         <v>161</v>
       </c>
-      <c r="K64" s="329"/>
-      <c r="L64" s="329" t="s">
+      <c r="K64" s="326"/>
+      <c r="L64" s="326" t="s">
         <v>162</v>
       </c>
       <c r="M64" s="67" t="s">
@@ -42342,7 +42326,7 @@
       <c r="D65" s="66" t="s">
         <v>131</v>
       </c>
-      <c r="E65" s="292">
+      <c r="E65" s="290">
         <v>330692005</v>
       </c>
       <c r="F65" s="66" t="s">
@@ -42360,8 +42344,8 @@
       <c r="J65" s="66" t="s">
         <v>242</v>
       </c>
-      <c r="K65" s="329"/>
-      <c r="L65" s="329" t="s">
+      <c r="K65" s="326"/>
+      <c r="L65" s="326" t="s">
         <v>406</v>
       </c>
       <c r="M65" s="67" t="s">
@@ -42390,7 +42374,7 @@
       <c r="D66" s="66" t="s">
         <v>353</v>
       </c>
-      <c r="E66" s="292">
+      <c r="E66" s="290">
         <v>215758699</v>
       </c>
       <c r="F66" s="66" t="s">
@@ -42408,8 +42392,8 @@
       <c r="J66" s="66" t="s">
         <v>956</v>
       </c>
-      <c r="K66" s="329"/>
-      <c r="L66" s="329" t="s">
+      <c r="K66" s="326"/>
+      <c r="L66" s="326" t="s">
         <v>957</v>
       </c>
       <c r="M66" s="67" t="s">
@@ -42438,7 +42422,7 @@
       <c r="D67" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="E67" s="292">
+      <c r="E67" s="290">
         <v>326763448</v>
       </c>
       <c r="F67" s="66" t="s">
@@ -42456,8 +42440,8 @@
       <c r="J67" s="66" t="s">
         <v>459</v>
       </c>
-      <c r="K67" s="329"/>
-      <c r="L67" s="329" t="s">
+      <c r="K67" s="326"/>
+      <c r="L67" s="326" t="s">
         <v>460</v>
       </c>
       <c r="M67" s="67" t="s">
@@ -42486,7 +42470,7 @@
       <c r="D68" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="E68" s="292">
+      <c r="E68" s="290">
         <v>216947564</v>
       </c>
       <c r="F68" s="66" t="s">
@@ -42504,8 +42488,8 @@
       <c r="J68" s="66" t="s">
         <v>709</v>
       </c>
-      <c r="K68" s="329"/>
-      <c r="L68" s="329" t="s">
+      <c r="K68" s="326"/>
+      <c r="L68" s="326" t="s">
         <v>710</v>
       </c>
       <c r="M68" s="67" t="s">
@@ -42534,7 +42518,7 @@
       <c r="D69" s="66" t="s">
         <v>238</v>
       </c>
-      <c r="E69" s="292">
+      <c r="E69" s="290">
         <v>331715987</v>
       </c>
       <c r="F69" s="66" t="s">
@@ -42552,10 +42536,10 @@
       <c r="J69" s="66" t="s">
         <v>242</v>
       </c>
-      <c r="K69" s="292">
+      <c r="K69" s="290">
         <v>10120380216</v>
       </c>
-      <c r="L69" s="329" t="s">
+      <c r="L69" s="326" t="s">
         <v>243</v>
       </c>
       <c r="M69" s="67" t="s">
@@ -42584,7 +42568,7 @@
       <c r="D70" s="66" t="s">
         <v>26</v>
       </c>
-      <c r="E70" s="292">
+      <c r="E70" s="290">
         <v>331736272</v>
       </c>
       <c r="F70" s="66" t="s">
@@ -42602,8 +42586,8 @@
       <c r="J70" s="66" t="s">
         <v>712</v>
       </c>
-      <c r="K70" s="329"/>
-      <c r="L70" s="329" t="s">
+      <c r="K70" s="326"/>
+      <c r="L70" s="326" t="s">
         <v>713</v>
       </c>
       <c r="M70" s="67" t="s">
@@ -42632,7 +42616,7 @@
       <c r="D71" s="66" t="s">
         <v>965</v>
       </c>
-      <c r="E71" s="292">
+      <c r="E71" s="290">
         <v>330776337</v>
       </c>
       <c r="F71" s="66" t="s">
@@ -42650,8 +42634,8 @@
       <c r="J71" s="66" t="s">
         <v>1268</v>
       </c>
-      <c r="K71" s="329"/>
-      <c r="L71" s="329" t="s">
+      <c r="K71" s="326"/>
+      <c r="L71" s="326" t="s">
         <v>1269</v>
       </c>
       <c r="M71" s="67" t="s">
@@ -42680,7 +42664,7 @@
       <c r="D72" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="E72" s="292">
+      <c r="E72" s="290">
         <v>215892027</v>
       </c>
       <c r="F72" s="66" t="s">
@@ -42698,8 +42682,8 @@
       <c r="J72" s="66" t="s">
         <v>678</v>
       </c>
-      <c r="K72" s="329"/>
-      <c r="L72" s="329" t="s">
+      <c r="K72" s="326"/>
+      <c r="L72" s="326" t="s">
         <v>679</v>
       </c>
       <c r="M72" s="67" t="s">
@@ -42728,7 +42712,7 @@
       <c r="D73" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="E73" s="292">
+      <c r="E73" s="290">
         <v>331044487</v>
       </c>
       <c r="F73" s="66" t="s">
@@ -42746,8 +42730,8 @@
       <c r="J73" s="66" t="s">
         <v>1089</v>
       </c>
-      <c r="K73" s="329"/>
-      <c r="L73" s="329" t="s">
+      <c r="K73" s="326"/>
+      <c r="L73" s="326" t="s">
         <v>1090</v>
       </c>
       <c r="M73" s="67" t="s">
@@ -42776,7 +42760,7 @@
       <c r="D74" s="66" t="s">
         <v>429</v>
       </c>
-      <c r="E74" s="292">
+      <c r="E74" s="290">
         <v>216681288</v>
       </c>
       <c r="F74" s="66" t="s">
@@ -42794,8 +42778,8 @@
       <c r="J74" s="66" t="s">
         <v>1125</v>
       </c>
-      <c r="K74" s="329"/>
-      <c r="L74" s="329" t="s">
+      <c r="K74" s="326"/>
+      <c r="L74" s="326" t="s">
         <v>1126</v>
       </c>
       <c r="M74" s="67" t="s">
@@ -42824,7 +42808,7 @@
       <c r="D75" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="E75" s="292">
+      <c r="E75" s="290">
         <v>216633263</v>
       </c>
       <c r="F75" s="66" t="s">
@@ -42842,8 +42826,8 @@
       <c r="J75" s="66" t="s">
         <v>318</v>
       </c>
-      <c r="K75" s="329"/>
-      <c r="L75" s="329" t="s">
+      <c r="K75" s="326"/>
+      <c r="L75" s="326" t="s">
         <v>319</v>
       </c>
       <c r="M75" s="67" t="s">
@@ -42872,7 +42856,7 @@
       <c r="D76" s="66" t="s">
         <v>9</v>
       </c>
-      <c r="E76" s="292">
+      <c r="E76" s="290">
         <v>330990045</v>
       </c>
       <c r="F76" s="66" t="s">
@@ -42890,8 +42874,8 @@
       <c r="J76" s="66" t="s">
         <v>776</v>
       </c>
-      <c r="K76" s="329"/>
-      <c r="L76" s="329" t="s">
+      <c r="K76" s="326"/>
+      <c r="L76" s="326" t="s">
         <v>777</v>
       </c>
       <c r="M76" s="67" t="s">
@@ -42920,7 +42904,7 @@
       <c r="D77" s="66" t="s">
         <v>429</v>
       </c>
-      <c r="E77" s="292">
+      <c r="E77" s="290">
         <v>216700583</v>
       </c>
       <c r="F77" s="66" t="s">
@@ -42938,8 +42922,8 @@
       <c r="J77" s="66" t="s">
         <v>898</v>
       </c>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329" t="s">
+      <c r="K77" s="326"/>
+      <c r="L77" s="326" t="s">
         <v>899</v>
       </c>
       <c r="M77" s="67" t="s">
@@ -42968,7 +42952,7 @@
       <c r="D78" s="69" t="s">
         <v>429</v>
       </c>
-      <c r="E78" s="294">
+      <c r="E78" s="292">
         <v>330985409</v>
       </c>
       <c r="F78" s="69" t="s">
@@ -42986,8 +42970,8 @@
       <c r="J78" s="69" t="s">
         <v>1075</v>
       </c>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330" t="s">
+      <c r="K78" s="327"/>
+      <c r="L78" s="327" t="s">
         <v>1076</v>
       </c>
       <c r="M78" s="70" t="s">
@@ -43016,7 +43000,7 @@
       <c r="D79" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="E79" s="295">
+      <c r="E79" s="293">
         <v>327948196</v>
       </c>
       <c r="F79" s="30" t="s">
@@ -43034,10 +43018,10 @@
       <c r="J79" s="30" t="s">
         <v>576</v>
       </c>
-      <c r="K79" s="295">
+      <c r="K79" s="293">
         <v>10118080609</v>
       </c>
-      <c r="L79" s="349" t="s">
+      <c r="L79" s="346" t="s">
         <v>577</v>
       </c>
       <c r="M79" s="31" t="s">
@@ -43066,7 +43050,7 @@
       <c r="D80" s="26" t="s">
         <v>353</v>
       </c>
-      <c r="E80" s="296">
+      <c r="E80" s="294">
         <v>216780171</v>
       </c>
       <c r="F80" s="26" t="s">
@@ -43114,7 +43098,7 @@
       <c r="D81" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="E81" s="296">
+      <c r="E81" s="294">
         <v>215942624</v>
       </c>
       <c r="F81" s="26" t="s">
@@ -43162,7 +43146,7 @@
       <c r="D82" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="E82" s="296">
+      <c r="E82" s="294">
         <v>216238089</v>
       </c>
       <c r="F82" s="26" t="s">
@@ -43210,7 +43194,7 @@
       <c r="D83" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="E83" s="296">
+      <c r="E83" s="294">
         <v>216365460</v>
       </c>
       <c r="F83" s="26" t="s">
@@ -43228,7 +43212,7 @@
       <c r="J83" s="26" t="s">
         <v>818</v>
       </c>
-      <c r="K83" s="296">
+      <c r="K83" s="294">
         <v>10115994200</v>
       </c>
       <c r="L83" s="23" t="s">
@@ -43260,7 +43244,7 @@
       <c r="D84" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="E84" s="296">
+      <c r="E84" s="294">
         <v>329741748</v>
       </c>
       <c r="F84" s="26" t="s">
@@ -43278,7 +43262,7 @@
       <c r="J84" s="26" t="s">
         <v>411</v>
       </c>
-      <c r="K84" s="296">
+      <c r="K84" s="294">
         <v>10122623542</v>
       </c>
       <c r="L84" s="23" t="s">
@@ -43310,7 +43294,7 @@
       <c r="D85" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="E85" s="296">
+      <c r="E85" s="294">
         <v>216701136</v>
       </c>
       <c r="F85" s="26" t="s">
@@ -43358,7 +43342,7 @@
       <c r="D86" s="26" t="s">
         <v>353</v>
       </c>
-      <c r="E86" s="296">
+      <c r="E86" s="294">
         <v>330846981</v>
       </c>
       <c r="F86" s="26" t="s">
@@ -43406,7 +43390,7 @@
       <c r="D87" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="E87" s="296">
+      <c r="E87" s="294">
         <v>330726647</v>
       </c>
       <c r="F87" s="26" t="s">
@@ -43454,7 +43438,7 @@
       <c r="D88" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="E88" s="296">
+      <c r="E88" s="294">
         <v>329220644</v>
       </c>
       <c r="F88" s="26" t="s">
@@ -43502,7 +43486,7 @@
       <c r="D89" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="E89" s="296">
+      <c r="E89" s="294">
         <v>217385988</v>
       </c>
       <c r="F89" s="26" t="s">
@@ -43550,7 +43534,7 @@
       <c r="D90" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="E90" s="296">
+      <c r="E90" s="294">
         <v>326730033</v>
       </c>
       <c r="F90" s="26" t="s">
@@ -43598,7 +43582,7 @@
       <c r="D91" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="E91" s="297">
+      <c r="E91" s="295">
         <v>329034565</v>
       </c>
       <c r="F91" s="28" t="s">
@@ -43616,8 +43600,8 @@
       <c r="J91" s="28" t="s">
         <v>286</v>
       </c>
-      <c r="K91" s="331"/>
-      <c r="L91" s="331" t="s">
+      <c r="K91" s="328"/>
+      <c r="L91" s="328" t="s">
         <v>287</v>
       </c>
       <c r="M91" s="24" t="s">
@@ -43633,53 +43617,53 @@
         <v>0.41736111111111113</v>
       </c>
     </row>
-    <row r="92" spans="1:16" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="354" t="s">
+    <row r="92" spans="1:16" ht="36.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A92" s="351" t="s">
         <v>1284</v>
       </c>
-      <c r="B92" s="355" t="s">
+      <c r="B92" s="352" t="s">
         <v>1290</v>
       </c>
-      <c r="C92" s="355" t="s">
+      <c r="C92" s="352" t="s">
         <v>0</v>
       </c>
-      <c r="D92" s="356" t="s">
+      <c r="D92" s="353" t="s">
         <v>1</v>
       </c>
-      <c r="E92" s="355" t="s">
+      <c r="E92" s="352" t="s">
         <v>1291</v>
       </c>
-      <c r="F92" s="356" t="s">
+      <c r="F92" s="353" t="s">
         <v>2</v>
       </c>
-      <c r="G92" s="356" t="s">
+      <c r="G92" s="353" t="s">
         <v>3</v>
       </c>
-      <c r="H92" s="356" t="s">
+      <c r="H92" s="353" t="s">
         <v>4</v>
       </c>
-      <c r="I92" s="356" t="s">
+      <c r="I92" s="353" t="s">
         <v>1292</v>
       </c>
-      <c r="J92" s="356" t="s">
+      <c r="J92" s="353" t="s">
         <v>1293</v>
       </c>
-      <c r="K92" s="357" t="s">
+      <c r="K92" s="354" t="s">
         <v>1294</v>
       </c>
-      <c r="L92" s="355" t="s">
+      <c r="L92" s="352" t="s">
         <v>6</v>
       </c>
-      <c r="M92" s="355" t="s">
+      <c r="M92" s="352" t="s">
         <v>5</v>
       </c>
-      <c r="N92" s="360" t="s">
+      <c r="N92" s="357" t="s">
         <v>1285</v>
       </c>
-      <c r="O92" s="355" t="s">
+      <c r="O92" s="352" t="s">
         <v>1286</v>
       </c>
-      <c r="P92" s="358" t="s">
+      <c r="P92" s="355" t="s">
         <v>1287</v>
       </c>
     </row>
@@ -43696,7 +43680,7 @@
       <c r="D93" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="E93" s="298">
+      <c r="E93" s="296">
         <v>319119384</v>
       </c>
       <c r="F93" s="19" t="s">
@@ -43714,7 +43698,7 @@
       <c r="J93" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="K93" s="298">
+      <c r="K93" s="296">
         <v>10011012615</v>
       </c>
       <c r="L93" s="21" t="s">
@@ -43746,7 +43730,7 @@
       <c r="D94" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="E94" s="299">
+      <c r="E94" s="297">
         <v>211713086</v>
       </c>
       <c r="F94" s="2" t="s">
@@ -43764,7 +43748,7 @@
       <c r="J94" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K94" s="299">
+      <c r="K94" s="297">
         <v>10056549465</v>
       </c>
       <c r="L94" s="7" t="s">
@@ -43796,7 +43780,7 @@
       <c r="D95" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="E95" s="299">
+      <c r="E95" s="297">
         <v>302571088</v>
       </c>
       <c r="F95" s="2" t="s">
@@ -43814,7 +43798,7 @@
       <c r="J95" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="K95" s="299">
+      <c r="K95" s="297">
         <v>10005815738</v>
       </c>
       <c r="L95" s="7" t="s">
@@ -43846,7 +43830,7 @@
       <c r="D96" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E96" s="299">
+      <c r="E96" s="297">
         <v>322648197</v>
       </c>
       <c r="F96" s="2" t="s">
@@ -43864,7 +43848,7 @@
       <c r="J96" s="2" t="s">
         <v>1245</v>
       </c>
-      <c r="K96" s="299">
+      <c r="K96" s="297">
         <v>10053899244</v>
       </c>
       <c r="L96" s="7" t="s">
@@ -43896,7 +43880,7 @@
       <c r="D97" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E97" s="299">
+      <c r="E97" s="297">
         <v>212392955</v>
       </c>
       <c r="F97" s="2" t="s">
@@ -43914,7 +43898,7 @@
       <c r="J97" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="K97" s="299">
+      <c r="K97" s="297">
         <v>10055884512</v>
       </c>
       <c r="L97" s="7" t="s">
@@ -43946,7 +43930,7 @@
       <c r="D98" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="E98" s="299">
+      <c r="E98" s="297">
         <v>324823830</v>
       </c>
       <c r="F98" s="2" t="s">
@@ -43964,7 +43948,7 @@
       <c r="J98" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="K98" s="299">
+      <c r="K98" s="297">
         <v>10080721259</v>
       </c>
       <c r="L98" s="7" t="s">
@@ -43996,7 +43980,7 @@
       <c r="D99" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="E99" s="299">
+      <c r="E99" s="297">
         <v>200558955</v>
       </c>
       <c r="F99" s="2" t="s">
@@ -44014,7 +43998,7 @@
       <c r="J99" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="K99" s="299">
+      <c r="K99" s="297">
         <v>10085167802</v>
       </c>
       <c r="L99" s="7" t="s">
@@ -44044,7 +44028,7 @@
         <v>8</v>
       </c>
       <c r="D100" s="2"/>
-      <c r="E100" s="299"/>
+      <c r="E100" s="297"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -44054,7 +44038,7 @@
       <c r="J100" s="48" t="s">
         <v>1307</v>
       </c>
-      <c r="K100" s="332">
+      <c r="K100" s="329">
         <v>10015647494</v>
       </c>
       <c r="L100" s="7"/>
@@ -44084,7 +44068,7 @@
       <c r="D101" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="E101" s="299">
+      <c r="E101" s="297">
         <v>322912338</v>
       </c>
       <c r="F101" s="2" t="s">
@@ -44102,7 +44086,7 @@
       <c r="J101" s="2" t="s">
         <v>1282</v>
       </c>
-      <c r="K101" s="299">
+      <c r="K101" s="297">
         <v>10056570986</v>
       </c>
       <c r="L101" s="7" t="s">
@@ -44134,7 +44118,7 @@
       <c r="D102" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E102" s="299">
+      <c r="E102" s="297">
         <v>213917487</v>
       </c>
       <c r="F102" s="2" t="s">
@@ -44152,7 +44136,7 @@
       <c r="J102" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="K102" s="299">
+      <c r="K102" s="297">
         <v>10092366919</v>
       </c>
       <c r="L102" s="7" t="s">
@@ -44184,7 +44168,7 @@
       <c r="D103" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E103" s="299">
+      <c r="E103" s="297">
         <v>213769607</v>
       </c>
       <c r="F103" s="2" t="s">
@@ -44202,7 +44186,7 @@
       <c r="J103" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="K103" s="299">
+      <c r="K103" s="297">
         <v>10105012483</v>
       </c>
       <c r="L103" s="7" t="s">
@@ -44234,7 +44218,7 @@
       <c r="D104" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E104" s="299">
+      <c r="E104" s="297">
         <v>214483505</v>
       </c>
       <c r="F104" s="2" t="s">
@@ -44252,7 +44236,7 @@
       <c r="J104" s="2" t="s">
         <v>933</v>
       </c>
-      <c r="K104" s="299">
+      <c r="K104" s="297">
         <v>10096368066</v>
       </c>
       <c r="L104" s="7" t="s">
@@ -44284,7 +44268,7 @@
       <c r="D105" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E105" s="299">
+      <c r="E105" s="297">
         <v>326038171</v>
       </c>
       <c r="F105" s="2" t="s">
@@ -44302,7 +44286,7 @@
       <c r="J105" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="K105" s="299">
+      <c r="K105" s="297">
         <v>10096374332</v>
       </c>
       <c r="L105" s="7" t="s">
@@ -44334,7 +44318,7 @@
       <c r="D106" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E106" s="299">
+      <c r="E106" s="297">
         <v>325272433</v>
       </c>
       <c r="F106" s="2" t="s">
@@ -44352,7 +44336,7 @@
       <c r="J106" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="K106" s="299">
+      <c r="K106" s="297">
         <v>10077042030</v>
       </c>
       <c r="L106" s="7" t="s">
@@ -44384,7 +44368,7 @@
       <c r="D107" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E107" s="299">
+      <c r="E107" s="297">
         <v>206749129</v>
       </c>
       <c r="F107" s="2" t="s">
@@ -44402,7 +44386,7 @@
       <c r="J107" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K107" s="299">
+      <c r="K107" s="297">
         <v>10112828461</v>
       </c>
       <c r="L107" s="7" t="s">
@@ -44434,7 +44418,7 @@
       <c r="D108" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E108" s="299">
+      <c r="E108" s="297">
         <v>200794238</v>
       </c>
       <c r="F108" s="2" t="s">
@@ -44452,7 +44436,7 @@
       <c r="J108" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="K108" s="299">
+      <c r="K108" s="297">
         <v>10009151528</v>
       </c>
       <c r="L108" s="7" t="s">
@@ -44484,7 +44468,7 @@
       <c r="D109" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E109" s="299">
+      <c r="E109" s="297">
         <v>214351017</v>
       </c>
       <c r="F109" s="2" t="s">
@@ -44502,7 +44486,7 @@
       <c r="J109" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="K109" s="299">
+      <c r="K109" s="297">
         <v>10107693323</v>
       </c>
       <c r="L109" s="7" t="s">
@@ -44534,7 +44518,7 @@
       <c r="D110" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E110" s="300">
+      <c r="E110" s="298">
         <v>211707799</v>
       </c>
       <c r="F110" s="6" t="s">
@@ -44552,7 +44536,7 @@
       <c r="J110" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="K110" s="300">
+      <c r="K110" s="298">
         <v>10112827754</v>
       </c>
       <c r="L110" s="8" t="s">
@@ -44584,7 +44568,7 @@
       <c r="D111" s="117" t="s">
         <v>33</v>
       </c>
-      <c r="E111" s="301">
+      <c r="E111" s="299">
         <v>214694952</v>
       </c>
       <c r="F111" s="117" t="s">
@@ -44602,10 +44586,10 @@
       <c r="J111" s="117" t="s">
         <v>250</v>
       </c>
-      <c r="K111" s="301">
+      <c r="K111" s="299">
         <v>10084064426</v>
       </c>
-      <c r="L111" s="351" t="s">
+      <c r="L111" s="348" t="s">
         <v>251</v>
       </c>
       <c r="M111" s="118" t="s">
@@ -44634,7 +44618,7 @@
       <c r="D112" s="122" t="s">
         <v>102</v>
       </c>
-      <c r="E112" s="302">
+      <c r="E112" s="300">
         <v>214785917</v>
       </c>
       <c r="F112" s="122" t="s">
@@ -44652,10 +44636,10 @@
       <c r="J112" s="122" t="s">
         <v>106</v>
       </c>
-      <c r="K112" s="302">
+      <c r="K112" s="300">
         <v>10096373726</v>
       </c>
-      <c r="L112" s="338" t="s">
+      <c r="L112" s="335" t="s">
         <v>107</v>
       </c>
       <c r="M112" s="123" t="s">
@@ -44684,7 +44668,7 @@
       <c r="D113" s="122" t="s">
         <v>376</v>
       </c>
-      <c r="E113" s="302">
+      <c r="E113" s="300">
         <v>214545287</v>
       </c>
       <c r="F113" s="122" t="s">
@@ -44702,10 +44686,10 @@
       <c r="J113" s="122" t="s">
         <v>1003</v>
       </c>
-      <c r="K113" s="302">
+      <c r="K113" s="300">
         <v>10082394410</v>
       </c>
-      <c r="L113" s="338" t="s">
+      <c r="L113" s="335" t="s">
         <v>1259</v>
       </c>
       <c r="M113" s="123" t="s">
@@ -44734,7 +44718,7 @@
       <c r="D114" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="E114" s="302">
+      <c r="E114" s="300">
         <v>326256302</v>
       </c>
       <c r="F114" s="122" t="s">
@@ -44752,10 +44736,10 @@
       <c r="J114" s="122" t="s">
         <v>1128</v>
       </c>
-      <c r="K114" s="302">
+      <c r="K114" s="300">
         <v>10092365101</v>
       </c>
-      <c r="L114" s="338" t="s">
+      <c r="L114" s="335" t="s">
         <v>1129</v>
       </c>
       <c r="M114" s="123" t="s">
@@ -44784,7 +44768,7 @@
       <c r="D115" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="E115" s="302">
+      <c r="E115" s="300">
         <v>325761062</v>
       </c>
       <c r="F115" s="122" t="s">
@@ -44802,10 +44786,10 @@
       <c r="J115" s="122" t="s">
         <v>727</v>
       </c>
-      <c r="K115" s="302">
+      <c r="K115" s="300">
         <v>10092366414</v>
       </c>
-      <c r="L115" s="338" t="s">
+      <c r="L115" s="335" t="s">
         <v>871</v>
       </c>
       <c r="M115" s="123" t="s">
@@ -44834,7 +44818,7 @@
       <c r="D116" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="E116" s="302">
+      <c r="E116" s="300">
         <v>326637030</v>
       </c>
       <c r="F116" s="122" t="s">
@@ -44852,10 +44836,10 @@
       <c r="J116" s="122" t="s">
         <v>1226</v>
       </c>
-      <c r="K116" s="302">
+      <c r="K116" s="300">
         <v>10092366212</v>
       </c>
-      <c r="L116" s="338" t="s">
+      <c r="L116" s="335" t="s">
         <v>1227</v>
       </c>
       <c r="M116" s="123" t="s">
@@ -44884,7 +44868,7 @@
       <c r="D117" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="E117" s="302">
+      <c r="E117" s="300">
         <v>326544095</v>
       </c>
       <c r="F117" s="122" t="s">
@@ -44902,10 +44886,10 @@
       <c r="J117" s="122" t="s">
         <v>171</v>
       </c>
-      <c r="K117" s="302">
+      <c r="K117" s="300">
         <v>10112824421</v>
       </c>
-      <c r="L117" s="338" t="s">
+      <c r="L117" s="335" t="s">
         <v>172</v>
       </c>
       <c r="M117" s="123" t="s">
@@ -44934,7 +44918,7 @@
       <c r="D118" s="122" t="s">
         <v>9</v>
       </c>
-      <c r="E118" s="302">
+      <c r="E118" s="300">
         <v>340078088</v>
       </c>
       <c r="F118" s="122" t="s">
@@ -44952,10 +44936,10 @@
       <c r="J118" s="122" t="s">
         <v>555</v>
       </c>
-      <c r="K118" s="302">
+      <c r="K118" s="300">
         <v>10111104487</v>
       </c>
-      <c r="L118" s="338" t="s">
+      <c r="L118" s="335" t="s">
         <v>556</v>
       </c>
       <c r="M118" s="123" t="s">
@@ -44984,7 +44968,7 @@
       <c r="D119" s="122" t="s">
         <v>73</v>
       </c>
-      <c r="E119" s="302">
+      <c r="E119" s="300">
         <v>328105887</v>
       </c>
       <c r="F119" s="122" t="s">
@@ -45002,10 +44986,10 @@
       <c r="J119" s="122" t="s">
         <v>609</v>
       </c>
-      <c r="K119" s="302">
+      <c r="K119" s="300">
         <v>10118080710</v>
       </c>
-      <c r="L119" s="338" t="s">
+      <c r="L119" s="335" t="s">
         <v>610</v>
       </c>
       <c r="M119" s="123" t="s">
@@ -45034,7 +45018,7 @@
       <c r="D120" s="122" t="s">
         <v>407</v>
       </c>
-      <c r="E120" s="302">
+      <c r="E120" s="300">
         <v>326584604</v>
       </c>
       <c r="F120" s="122" t="s">
@@ -45052,10 +45036,10 @@
       <c r="J120" s="122" t="s">
         <v>592</v>
       </c>
-      <c r="K120" s="302">
+      <c r="K120" s="300">
         <v>10100358103</v>
       </c>
-      <c r="L120" s="338" t="s">
+      <c r="L120" s="335" t="s">
         <v>593</v>
       </c>
       <c r="M120" s="123" t="s">
@@ -45084,7 +45068,7 @@
       <c r="D121" s="122" t="s">
         <v>33</v>
       </c>
-      <c r="E121" s="302">
+      <c r="E121" s="300">
         <v>215132010</v>
       </c>
       <c r="F121" s="122" t="s">
@@ -45102,10 +45086,10 @@
       <c r="J121" s="122" t="s">
         <v>210</v>
       </c>
-      <c r="K121" s="302">
+      <c r="K121" s="300">
         <v>10118080407</v>
       </c>
-      <c r="L121" s="338" t="s">
+      <c r="L121" s="335" t="s">
         <v>1023</v>
       </c>
       <c r="M121" s="123" t="s">
@@ -45134,7 +45118,7 @@
       <c r="D122" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="E122" s="302">
+      <c r="E122" s="300">
         <v>326451655</v>
       </c>
       <c r="F122" s="122" t="s">
@@ -45152,10 +45136,10 @@
       <c r="J122" s="122" t="s">
         <v>980</v>
       </c>
-      <c r="K122" s="302">
+      <c r="K122" s="300">
         <v>10118915213</v>
       </c>
-      <c r="L122" s="338" t="s">
+      <c r="L122" s="335" t="s">
         <v>1104</v>
       </c>
       <c r="M122" s="123" t="s">
@@ -45184,7 +45168,7 @@
       <c r="D123" s="122" t="s">
         <v>407</v>
       </c>
-      <c r="E123" s="302">
+      <c r="E123" s="300">
         <v>327653598</v>
       </c>
       <c r="F123" s="122" t="s">
@@ -45202,10 +45186,10 @@
       <c r="J123" s="122" t="s">
         <v>884</v>
       </c>
-      <c r="K123" s="302">
+      <c r="K123" s="300">
         <v>10126118572</v>
       </c>
-      <c r="L123" s="338" t="s">
+      <c r="L123" s="335" t="s">
         <v>885</v>
       </c>
       <c r="M123" s="123" t="s">
@@ -45235,7 +45219,7 @@
       <c r="D124" s="122" t="s">
         <v>407</v>
       </c>
-      <c r="E124" s="302">
+      <c r="E124" s="300">
         <v>215200908</v>
       </c>
       <c r="F124" s="122" t="s">
@@ -45253,10 +45237,10 @@
       <c r="J124" s="122" t="s">
         <v>743</v>
       </c>
-      <c r="K124" s="302">
+      <c r="K124" s="300">
         <v>10122412465</v>
       </c>
-      <c r="L124" s="338" t="s">
+      <c r="L124" s="335" t="s">
         <v>744</v>
       </c>
       <c r="M124" s="123" t="s">
@@ -45286,7 +45270,7 @@
       <c r="D125" s="122" t="s">
         <v>965</v>
       </c>
-      <c r="E125" s="302">
+      <c r="E125" s="300">
         <v>326487683</v>
       </c>
       <c r="F125" s="122" t="s">
@@ -45304,10 +45288,10 @@
       <c r="J125" s="122" t="s">
         <v>1261</v>
       </c>
-      <c r="K125" s="302">
+      <c r="K125" s="300">
         <v>10112824623</v>
       </c>
-      <c r="L125" s="338" t="s">
+      <c r="L125" s="335" t="s">
         <v>1262</v>
       </c>
       <c r="M125" s="123" t="s">
@@ -45337,7 +45321,7 @@
       <c r="D126" s="122" t="s">
         <v>96</v>
       </c>
-      <c r="E126" s="302">
+      <c r="E126" s="300">
         <v>328454293</v>
       </c>
       <c r="F126" s="122" t="s">
@@ -45355,10 +45339,10 @@
       <c r="J126" s="122" t="s">
         <v>696</v>
       </c>
-      <c r="K126" s="302">
+      <c r="K126" s="300">
         <v>10126117764</v>
       </c>
-      <c r="L126" s="338" t="s">
+      <c r="L126" s="335" t="s">
         <v>697</v>
       </c>
       <c r="M126" s="123" t="s">
@@ -45387,7 +45371,7 @@
       <c r="D127" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="E127" s="302">
+      <c r="E127" s="300">
         <v>215300807</v>
       </c>
       <c r="F127" s="122" t="s">
@@ -45405,10 +45389,10 @@
       <c r="J127" s="122" t="s">
         <v>1111</v>
       </c>
-      <c r="K127" s="302">
+      <c r="K127" s="300">
         <v>10126112108</v>
       </c>
-      <c r="L127" s="338" t="s">
+      <c r="L127" s="335" t="s">
         <v>1112</v>
       </c>
       <c r="M127" s="123" t="s">
@@ -45437,7 +45421,7 @@
       <c r="D128" s="122" t="s">
         <v>407</v>
       </c>
-      <c r="E128" s="302">
+      <c r="E128" s="300">
         <v>216000331</v>
       </c>
       <c r="F128" s="122" t="s">
@@ -45455,10 +45439,10 @@
       <c r="J128" s="122" t="s">
         <v>1122</v>
       </c>
-      <c r="K128" s="302">
+      <c r="K128" s="300">
         <v>10122413374</v>
       </c>
-      <c r="L128" s="338" t="s">
+      <c r="L128" s="335" t="s">
         <v>1123</v>
       </c>
       <c r="M128" s="123" t="s">
@@ -45487,7 +45471,7 @@
       <c r="D129" s="132" t="s">
         <v>519</v>
       </c>
-      <c r="E129" s="303">
+      <c r="E129" s="301">
         <v>326227733</v>
       </c>
       <c r="F129" s="132" t="s">
@@ -45505,10 +45489,10 @@
       <c r="J129" s="132" t="s">
         <v>721</v>
       </c>
-      <c r="K129" s="303">
+      <c r="K129" s="301">
         <v>10126119380</v>
       </c>
-      <c r="L129" s="352" t="s">
+      <c r="L129" s="349" t="s">
         <v>722</v>
       </c>
       <c r="M129" s="133" t="s">
@@ -45535,7 +45519,7 @@
         <v>101</v>
       </c>
       <c r="D130" s="132"/>
-      <c r="E130" s="303">
+      <c r="E130" s="301">
         <v>215317108</v>
       </c>
       <c r="F130" s="132" t="s">
@@ -45551,16 +45535,16 @@
       <c r="J130" s="132" t="s">
         <v>1322</v>
       </c>
-      <c r="K130" s="303">
+      <c r="K130" s="301">
         <v>10119332717</v>
       </c>
-      <c r="L130" s="429">
+      <c r="L130" s="423">
         <v>38598</v>
       </c>
       <c r="M130" s="133" t="s">
         <v>15</v>
       </c>
-      <c r="N130" s="428" t="s">
+      <c r="N130" s="422" t="s">
         <v>1323</v>
       </c>
       <c r="O130" s="135" t="s">
@@ -45583,7 +45567,7 @@
       <c r="D131" s="73" t="s">
         <v>33</v>
       </c>
-      <c r="E131" s="291">
+      <c r="E131" s="289">
         <v>206476624</v>
       </c>
       <c r="F131" s="73" t="s">
@@ -45601,10 +45585,10 @@
       <c r="J131" s="73" t="s">
         <v>880</v>
       </c>
-      <c r="K131" s="291">
+      <c r="K131" s="289">
         <v>10009828710</v>
       </c>
-      <c r="L131" s="328" t="s">
+      <c r="L131" s="325" t="s">
         <v>1280</v>
       </c>
       <c r="M131" s="64" t="s">
@@ -45633,7 +45617,7 @@
       <c r="D132" s="66" t="s">
         <v>66</v>
       </c>
-      <c r="E132" s="292">
+      <c r="E132" s="290">
         <v>207484221</v>
       </c>
       <c r="F132" s="66" t="s">
@@ -45651,10 +45635,10 @@
       <c r="J132" s="66" t="s">
         <v>830</v>
       </c>
-      <c r="K132" s="292">
+      <c r="K132" s="290">
         <v>10088431042</v>
       </c>
-      <c r="L132" s="329" t="s">
+      <c r="L132" s="326" t="s">
         <v>831</v>
       </c>
       <c r="M132" s="67" t="s">
@@ -45683,7 +45667,7 @@
       <c r="D133" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="E133" s="292">
+      <c r="E133" s="290">
         <v>213131451</v>
       </c>
       <c r="F133" s="66" t="s">
@@ -45701,10 +45685,10 @@
       <c r="J133" s="66" t="s">
         <v>1182</v>
       </c>
-      <c r="K133" s="292">
+      <c r="K133" s="290">
         <v>10071222737</v>
       </c>
-      <c r="L133" s="329" t="s">
+      <c r="L133" s="326" t="s">
         <v>1183</v>
       </c>
       <c r="M133" s="67" t="s">
@@ -45733,7 +45717,7 @@
       <c r="D134" s="138" t="s">
         <v>66</v>
       </c>
-      <c r="E134" s="304">
+      <c r="E134" s="302">
         <v>209618446</v>
       </c>
       <c r="F134" s="138" t="s">
@@ -45751,10 +45735,10 @@
       <c r="J134" s="138" t="s">
         <v>903</v>
       </c>
-      <c r="K134" s="304">
+      <c r="K134" s="302">
         <v>10084183553</v>
       </c>
-      <c r="L134" s="353" t="s">
+      <c r="L134" s="350" t="s">
         <v>904</v>
       </c>
       <c r="M134" s="139" t="s">
@@ -45783,7 +45767,7 @@
       <c r="D135" s="33" t="s">
         <v>376</v>
       </c>
-      <c r="E135" s="305">
+      <c r="E135" s="303">
         <v>326160843</v>
       </c>
       <c r="F135" s="33" t="s">
@@ -45801,7 +45785,7 @@
       <c r="J135" s="33" t="s">
         <v>627</v>
       </c>
-      <c r="K135" s="305">
+      <c r="K135" s="303">
         <v>10082396430</v>
       </c>
       <c r="L135" s="35" t="s">
@@ -45833,7 +45817,7 @@
       <c r="D136" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="E136" s="306">
+      <c r="E136" s="304">
         <v>215091315</v>
       </c>
       <c r="F136" s="37" t="s">
@@ -45851,7 +45835,7 @@
       <c r="J136" s="37" t="s">
         <v>497</v>
       </c>
-      <c r="K136" s="306">
+      <c r="K136" s="304">
         <v>10118080205</v>
       </c>
       <c r="L136" s="39" t="s">
@@ -45883,7 +45867,7 @@
       <c r="D137" s="37" t="s">
         <v>1138</v>
       </c>
-      <c r="E137" s="306">
+      <c r="E137" s="304">
         <v>213472475</v>
       </c>
       <c r="F137" s="37" t="s">
@@ -45901,7 +45885,7 @@
       <c r="J137" s="37" t="s">
         <v>1141</v>
       </c>
-      <c r="K137" s="306">
+      <c r="K137" s="304">
         <v>10117764246</v>
       </c>
       <c r="L137" s="39" t="s">
@@ -45933,7 +45917,7 @@
       <c r="D138" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="E138" s="306">
+      <c r="E138" s="304">
         <v>215240870</v>
       </c>
       <c r="F138" s="37" t="s">
@@ -45951,7 +45935,7 @@
       <c r="J138" s="37" t="s">
         <v>1175</v>
       </c>
-      <c r="K138" s="306">
+      <c r="K138" s="304">
         <v>10126111502</v>
       </c>
       <c r="L138" s="39" t="s">
@@ -45983,7 +45967,7 @@
       <c r="D139" s="37" t="s">
         <v>227</v>
       </c>
-      <c r="E139" s="306">
+      <c r="E139" s="304">
         <v>326985983</v>
       </c>
       <c r="F139" s="37" t="s">
@@ -46001,7 +45985,7 @@
       <c r="J139" s="37" t="s">
         <v>1273</v>
       </c>
-      <c r="K139" s="306">
+      <c r="K139" s="304">
         <v>10118080306</v>
       </c>
       <c r="L139" s="39" t="s">
@@ -46033,7 +46017,7 @@
       <c r="D140" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E140" s="306">
+      <c r="E140" s="304">
         <v>215342320</v>
       </c>
       <c r="F140" s="37" t="s">
@@ -46051,7 +46035,7 @@
       <c r="J140" s="37" t="s">
         <v>1223</v>
       </c>
-      <c r="K140" s="306">
+      <c r="K140" s="304">
         <v>10126113320</v>
       </c>
       <c r="L140" s="39" t="s">
@@ -46083,7 +46067,7 @@
       <c r="D141" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="E141" s="307">
+      <c r="E141" s="305">
         <v>214973562</v>
       </c>
       <c r="F141" s="45" t="s">
@@ -46101,7 +46085,7 @@
       <c r="J141" s="45" t="s">
         <v>1038</v>
       </c>
-      <c r="K141" s="307">
+      <c r="K141" s="305">
         <v>10126111300</v>
       </c>
       <c r="L141" s="47" t="s">
@@ -46120,7 +46104,7 @@
         <v>0.47986111111111113</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" ht="36.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A142" s="157" t="s">
         <v>1284</v>
       </c>
@@ -46151,7 +46135,7 @@
       <c r="J142" s="4" t="s">
         <v>1293</v>
       </c>
-      <c r="K142" s="326" t="s">
+      <c r="K142" s="324" t="s">
         <v>1294</v>
       </c>
       <c r="L142" s="285" t="s">
@@ -46160,7 +46144,7 @@
       <c r="M142" s="285" t="s">
         <v>5</v>
       </c>
-      <c r="N142" s="359" t="s">
+      <c r="N142" s="356" t="s">
         <v>1285</v>
       </c>
       <c r="O142" s="285" t="s">
@@ -46183,7 +46167,7 @@
       <c r="D143" s="143" t="s">
         <v>1077</v>
       </c>
-      <c r="E143" s="308">
+      <c r="E143" s="306">
         <v>217899343</v>
       </c>
       <c r="F143" s="143" t="s">
@@ -46201,8 +46185,8 @@
       <c r="J143" s="143" t="s">
         <v>1093</v>
       </c>
-      <c r="K143" s="333"/>
-      <c r="L143" s="333" t="s">
+      <c r="K143" s="330"/>
+      <c r="L143" s="330" t="s">
         <v>1094</v>
       </c>
       <c r="M143" s="144" t="s">
@@ -46231,7 +46215,7 @@
       <c r="D144" s="148" t="s">
         <v>370</v>
       </c>
-      <c r="E144" s="309">
+      <c r="E144" s="307">
         <v>217997402</v>
       </c>
       <c r="F144" s="148" t="s">
@@ -46249,8 +46233,8 @@
       <c r="J144" s="148" t="s">
         <v>732</v>
       </c>
-      <c r="K144" s="334"/>
-      <c r="L144" s="334" t="s">
+      <c r="K144" s="331"/>
+      <c r="L144" s="331" t="s">
         <v>1171</v>
       </c>
       <c r="M144" s="149" t="s">
@@ -46279,7 +46263,7 @@
       <c r="D145" s="148" t="s">
         <v>33</v>
       </c>
-      <c r="E145" s="309">
+      <c r="E145" s="307">
         <v>333734515</v>
       </c>
       <c r="F145" s="148" t="s">
@@ -46297,8 +46281,8 @@
       <c r="J145" s="148" t="s">
         <v>205</v>
       </c>
-      <c r="K145" s="334"/>
-      <c r="L145" s="334" t="s">
+      <c r="K145" s="331"/>
+      <c r="L145" s="331" t="s">
         <v>206</v>
       </c>
       <c r="M145" s="149" t="s">
@@ -46327,7 +46311,7 @@
       <c r="D146" s="148" t="s">
         <v>407</v>
       </c>
-      <c r="E146" s="309">
+      <c r="E146" s="307">
         <v>334333408</v>
       </c>
       <c r="F146" s="148" t="s">
@@ -46345,8 +46329,8 @@
       <c r="J146" s="148" t="s">
         <v>804</v>
       </c>
-      <c r="K146" s="334"/>
-      <c r="L146" s="334" t="s">
+      <c r="K146" s="331"/>
+      <c r="L146" s="331" t="s">
         <v>805</v>
       </c>
       <c r="M146" s="149" t="s">
@@ -46375,7 +46359,7 @@
       <c r="D147" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="E147" s="309">
+      <c r="E147" s="307">
         <v>332888759</v>
       </c>
       <c r="F147" s="148" t="s">
@@ -46393,8 +46377,8 @@
       <c r="J147" s="148" t="s">
         <v>210</v>
       </c>
-      <c r="K147" s="334"/>
-      <c r="L147" s="334" t="s">
+      <c r="K147" s="331"/>
+      <c r="L147" s="331" t="s">
         <v>211</v>
       </c>
       <c r="M147" s="149" t="s">
@@ -46423,7 +46407,7 @@
       <c r="D148" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="E148" s="309">
+      <c r="E148" s="307">
         <v>331188870</v>
       </c>
       <c r="F148" s="148" t="s">
@@ -46441,8 +46425,8 @@
       <c r="J148" s="148" t="s">
         <v>440</v>
       </c>
-      <c r="K148" s="334"/>
-      <c r="L148" s="334" t="s">
+      <c r="K148" s="331"/>
+      <c r="L148" s="331" t="s">
         <v>650</v>
       </c>
       <c r="M148" s="149" t="s">
@@ -46471,7 +46455,7 @@
       <c r="D149" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="E149" s="309">
+      <c r="E149" s="307">
         <v>217457746</v>
       </c>
       <c r="F149" s="148" t="s">
@@ -46489,8 +46473,8 @@
       <c r="J149" s="148" t="s">
         <v>801</v>
       </c>
-      <c r="K149" s="334"/>
-      <c r="L149" s="334" t="s">
+      <c r="K149" s="331"/>
+      <c r="L149" s="331" t="s">
         <v>802</v>
       </c>
       <c r="M149" s="149" t="s">
@@ -46519,7 +46503,7 @@
       <c r="D150" s="148" t="s">
         <v>376</v>
       </c>
-      <c r="E150" s="309">
+      <c r="E150" s="307">
         <v>331251082</v>
       </c>
       <c r="F150" s="148" t="s">
@@ -46537,8 +46521,8 @@
       <c r="J150" s="148" t="s">
         <v>907</v>
       </c>
-      <c r="K150" s="334"/>
-      <c r="L150" s="334" t="s">
+      <c r="K150" s="331"/>
+      <c r="L150" s="331" t="s">
         <v>908</v>
       </c>
       <c r="M150" s="149" t="s">
@@ -46567,7 +46551,7 @@
       <c r="D151" s="148" t="s">
         <v>227</v>
       </c>
-      <c r="E151" s="309">
+      <c r="E151" s="307">
         <v>328378799</v>
       </c>
       <c r="F151" s="148" t="s">
@@ -46585,8 +46569,8 @@
       <c r="J151" s="148" t="s">
         <v>620</v>
       </c>
-      <c r="K151" s="334"/>
-      <c r="L151" s="334" t="s">
+      <c r="K151" s="331"/>
+      <c r="L151" s="331" t="s">
         <v>621</v>
       </c>
       <c r="M151" s="149" t="s">
@@ -46615,7 +46599,7 @@
       <c r="D152" s="148" t="s">
         <v>407</v>
       </c>
-      <c r="E152" s="309">
+      <c r="E152" s="307">
         <v>334122074</v>
       </c>
       <c r="F152" s="148" t="s">
@@ -46633,8 +46617,8 @@
       <c r="J152" s="148" t="s">
         <v>809</v>
       </c>
-      <c r="K152" s="334"/>
-      <c r="L152" s="334" t="s">
+      <c r="K152" s="331"/>
+      <c r="L152" s="331" t="s">
         <v>810</v>
       </c>
       <c r="M152" s="149" t="s">
@@ -46663,7 +46647,7 @@
       <c r="D153" s="148" t="s">
         <v>353</v>
       </c>
-      <c r="E153" s="309">
+      <c r="E153" s="307">
         <v>333688174</v>
       </c>
       <c r="F153" s="148" t="s">
@@ -46681,8 +46665,8 @@
       <c r="J153" s="148" t="s">
         <v>927</v>
       </c>
-      <c r="K153" s="334"/>
-      <c r="L153" s="334" t="s">
+      <c r="K153" s="331"/>
+      <c r="L153" s="331" t="s">
         <v>621</v>
       </c>
       <c r="M153" s="149" t="s">
@@ -46711,7 +46695,7 @@
       <c r="D154" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="E154" s="309">
+      <c r="E154" s="307">
         <v>333697704</v>
       </c>
       <c r="F154" s="148" t="s">
@@ -46729,8 +46713,8 @@
       <c r="J154" s="148" t="s">
         <v>424</v>
       </c>
-      <c r="K154" s="334"/>
-      <c r="L154" s="334" t="s">
+      <c r="K154" s="331"/>
+      <c r="L154" s="331" t="s">
         <v>425</v>
       </c>
       <c r="M154" s="149" t="s">
@@ -46759,7 +46743,7 @@
       <c r="D155" s="148" t="s">
         <v>131</v>
       </c>
-      <c r="E155" s="309">
+      <c r="E155" s="307">
         <v>333611259</v>
       </c>
       <c r="F155" s="148" t="s">
@@ -46777,8 +46761,8 @@
       <c r="J155" s="148" t="s">
         <v>1100</v>
       </c>
-      <c r="K155" s="334"/>
-      <c r="L155" s="334" t="s">
+      <c r="K155" s="331"/>
+      <c r="L155" s="331" t="s">
         <v>1101</v>
       </c>
       <c r="M155" s="149" t="s">
@@ -46807,7 +46791,7 @@
       <c r="D156" s="148" t="s">
         <v>131</v>
       </c>
-      <c r="E156" s="309">
+      <c r="E156" s="307">
         <v>218504686</v>
       </c>
       <c r="F156" s="148" t="s">
@@ -46825,8 +46809,8 @@
       <c r="J156" s="148" t="s">
         <v>1193</v>
       </c>
-      <c r="K156" s="334"/>
-      <c r="L156" s="334" t="s">
+      <c r="K156" s="331"/>
+      <c r="L156" s="331" t="s">
         <v>1194</v>
       </c>
       <c r="M156" s="149" t="s">
@@ -46855,7 +46839,7 @@
       <c r="D157" s="148" t="s">
         <v>131</v>
       </c>
-      <c r="E157" s="309">
+      <c r="E157" s="307">
         <v>333607877</v>
       </c>
       <c r="F157" s="148" t="s">
@@ -46873,8 +46857,8 @@
       <c r="J157" s="148" t="s">
         <v>701</v>
       </c>
-      <c r="K157" s="334"/>
-      <c r="L157" s="334" t="s">
+      <c r="K157" s="331"/>
+      <c r="L157" s="331" t="s">
         <v>702</v>
       </c>
       <c r="M157" s="149" t="s">
@@ -46903,7 +46887,7 @@
       <c r="D158" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="E158" s="309">
+      <c r="E158" s="307">
         <v>331177170</v>
       </c>
       <c r="F158" s="148" t="s">
@@ -46921,8 +46905,8 @@
       <c r="J158" s="148" t="s">
         <v>517</v>
       </c>
-      <c r="K158" s="334"/>
-      <c r="L158" s="334" t="s">
+      <c r="K158" s="331"/>
+      <c r="L158" s="331" t="s">
         <v>518</v>
       </c>
       <c r="M158" s="149" t="s">
@@ -46951,7 +46935,7 @@
       <c r="D159" s="148" t="s">
         <v>96</v>
       </c>
-      <c r="E159" s="309">
+      <c r="E159" s="307">
         <v>333576346</v>
       </c>
       <c r="F159" s="148" t="s">
@@ -46969,8 +46953,8 @@
       <c r="J159" s="148" t="s">
         <v>512</v>
       </c>
-      <c r="K159" s="334"/>
-      <c r="L159" s="334" t="s">
+      <c r="K159" s="331"/>
+      <c r="L159" s="331" t="s">
         <v>914</v>
       </c>
       <c r="M159" s="149" t="s">
@@ -46999,7 +46983,7 @@
       <c r="D160" s="148" t="s">
         <v>96</v>
       </c>
-      <c r="E160" s="309">
+      <c r="E160" s="307">
         <v>332874247</v>
       </c>
       <c r="F160" s="148" t="s">
@@ -47017,8 +47001,8 @@
       <c r="J160" s="148" t="s">
         <v>450</v>
       </c>
-      <c r="K160" s="334"/>
-      <c r="L160" s="334" t="s">
+      <c r="K160" s="331"/>
+      <c r="L160" s="331" t="s">
         <v>451</v>
       </c>
       <c r="M160" s="149" t="s">
@@ -47047,7 +47031,7 @@
       <c r="D161" s="148" t="s">
         <v>66</v>
       </c>
-      <c r="E161" s="309">
+      <c r="E161" s="307">
         <v>333036002</v>
       </c>
       <c r="F161" s="148" t="s">
@@ -47065,8 +47049,8 @@
       <c r="J161" s="148" t="s">
         <v>70</v>
       </c>
-      <c r="K161" s="334"/>
-      <c r="L161" s="334" t="s">
+      <c r="K161" s="331"/>
+      <c r="L161" s="331" t="s">
         <v>71</v>
       </c>
       <c r="M161" s="149" t="s">
@@ -47095,7 +47079,7 @@
       <c r="D162" s="148" t="s">
         <v>59</v>
       </c>
-      <c r="E162" s="309">
+      <c r="E162" s="307">
         <v>218248177</v>
       </c>
       <c r="F162" s="148" t="s">
@@ -47113,10 +47097,10 @@
       <c r="J162" s="148" t="s">
         <v>1211</v>
       </c>
-      <c r="K162" s="309">
+      <c r="K162" s="307">
         <v>10119027165</v>
       </c>
-      <c r="L162" s="334" t="s">
+      <c r="L162" s="331" t="s">
         <v>1212</v>
       </c>
       <c r="M162" s="149" t="s">
@@ -47145,7 +47129,7 @@
       <c r="D163" s="148" t="s">
         <v>96</v>
       </c>
-      <c r="E163" s="309">
+      <c r="E163" s="307">
         <v>333615771</v>
       </c>
       <c r="F163" s="148" t="s">
@@ -47163,8 +47147,8 @@
       <c r="J163" s="148" t="s">
         <v>13</v>
       </c>
-      <c r="K163" s="334"/>
-      <c r="L163" s="334" t="s">
+      <c r="K163" s="331"/>
+      <c r="L163" s="331" t="s">
         <v>364</v>
       </c>
       <c r="M163" s="149" t="s">
@@ -47193,7 +47177,7 @@
       <c r="D164" s="148" t="s">
         <v>131</v>
       </c>
-      <c r="E164" s="309">
+      <c r="E164" s="307">
         <v>333579761</v>
       </c>
       <c r="F164" s="148" t="s">
@@ -47211,8 +47195,8 @@
       <c r="J164" s="148" t="s">
         <v>295</v>
       </c>
-      <c r="K164" s="334"/>
-      <c r="L164" s="334" t="s">
+      <c r="K164" s="331"/>
+      <c r="L164" s="331" t="s">
         <v>296</v>
       </c>
       <c r="M164" s="149" t="s">
@@ -47241,7 +47225,7 @@
       <c r="D165" s="148" t="s">
         <v>96</v>
       </c>
-      <c r="E165" s="309">
+      <c r="E165" s="307">
         <v>333633667</v>
       </c>
       <c r="F165" s="148" t="s">
@@ -47259,8 +47243,8 @@
       <c r="J165" s="148" t="s">
         <v>686</v>
       </c>
-      <c r="K165" s="334"/>
-      <c r="L165" s="334" t="s">
+      <c r="K165" s="331"/>
+      <c r="L165" s="331" t="s">
         <v>687</v>
       </c>
       <c r="M165" s="149" t="s">
@@ -47289,7 +47273,7 @@
       <c r="D166" s="148" t="s">
         <v>59</v>
       </c>
-      <c r="E166" s="309">
+      <c r="E166" s="307">
         <v>333533636</v>
       </c>
       <c r="F166" s="148" t="s">
@@ -47307,8 +47291,8 @@
       <c r="J166" s="148" t="s">
         <v>727</v>
       </c>
-      <c r="K166" s="334"/>
-      <c r="L166" s="334" t="s">
+      <c r="K166" s="331"/>
+      <c r="L166" s="331" t="s">
         <v>728</v>
       </c>
       <c r="M166" s="149" t="s">
@@ -47337,7 +47321,7 @@
       <c r="D167" s="153" t="s">
         <v>429</v>
       </c>
-      <c r="E167" s="310">
+      <c r="E167" s="308">
         <v>333585305</v>
       </c>
       <c r="F167" s="153" t="s">
@@ -47355,8 +47339,8 @@
       <c r="J167" s="153" t="s">
         <v>1146</v>
       </c>
-      <c r="K167" s="335"/>
-      <c r="L167" s="335" t="s">
+      <c r="K167" s="332"/>
+      <c r="L167" s="332" t="s">
         <v>1147</v>
       </c>
       <c r="M167" s="154" t="s">
@@ -47386,7 +47370,7 @@
       <c r="D168" s="33" t="s">
         <v>353</v>
       </c>
-      <c r="E168" s="305">
+      <c r="E168" s="303">
         <v>331579938</v>
       </c>
       <c r="F168" s="33" t="s">
@@ -47434,7 +47418,7 @@
       <c r="D169" s="37" t="s">
         <v>66</v>
       </c>
-      <c r="E169" s="306">
+      <c r="E169" s="304">
         <v>331810929</v>
       </c>
       <c r="F169" s="37" t="s">
@@ -47483,7 +47467,7 @@
       <c r="D170" s="37" t="s">
         <v>407</v>
       </c>
-      <c r="E170" s="306">
+      <c r="E170" s="304">
         <v>218558575</v>
       </c>
       <c r="F170" s="37" t="s">
@@ -47531,7 +47515,7 @@
       <c r="D171" s="37" t="s">
         <v>227</v>
       </c>
-      <c r="E171" s="306">
+      <c r="E171" s="304">
         <v>331695577</v>
       </c>
       <c r="F171" s="37" t="s">
@@ -47579,7 +47563,7 @@
       <c r="D172" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="E172" s="311">
+      <c r="E172" s="309">
         <v>218049336</v>
       </c>
       <c r="F172" s="41" t="s">
@@ -47614,7 +47598,7 @@
         <v>0.56319444444444444</v>
       </c>
     </row>
-    <row r="173" spans="1:16" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16" ht="36.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A173" s="157" t="s">
         <v>1284</v>
       </c>
@@ -47645,7 +47629,7 @@
       <c r="J173" s="4" t="s">
         <v>1293</v>
       </c>
-      <c r="K173" s="326" t="s">
+      <c r="K173" s="324" t="s">
         <v>1294</v>
       </c>
       <c r="L173" s="285" t="s">
@@ -47654,7 +47638,7 @@
       <c r="M173" s="285" t="s">
         <v>5</v>
       </c>
-      <c r="N173" s="359" t="s">
+      <c r="N173" s="356" t="s">
         <v>1285</v>
       </c>
       <c r="O173" s="285" t="s">
@@ -47677,7 +47661,7 @@
       <c r="D174" s="201" t="s">
         <v>227</v>
       </c>
-      <c r="E174" s="312">
+      <c r="E174" s="310">
         <v>332160738</v>
       </c>
       <c r="F174" s="201" t="s">
@@ -47725,7 +47709,7 @@
       <c r="D175" s="205" t="s">
         <v>19</v>
       </c>
-      <c r="E175" s="313">
+      <c r="E175" s="311">
         <v>331144709</v>
       </c>
       <c r="F175" s="205" t="s">
@@ -47773,7 +47757,7 @@
       <c r="D176" s="205" t="s">
         <v>276</v>
       </c>
-      <c r="E176" s="313">
+      <c r="E176" s="311">
         <v>217138437</v>
       </c>
       <c r="F176" s="205" t="s">
@@ -47821,7 +47805,7 @@
       <c r="D177" s="205" t="s">
         <v>333</v>
       </c>
-      <c r="E177" s="313">
+      <c r="E177" s="311">
         <v>331108662</v>
       </c>
       <c r="F177" s="205" t="s">
@@ -47869,7 +47853,7 @@
       <c r="D178" s="205" t="s">
         <v>131</v>
       </c>
-      <c r="E178" s="313">
+      <c r="E178" s="311">
         <v>331970657</v>
       </c>
       <c r="F178" s="205" t="s">
@@ -47917,7 +47901,7 @@
       <c r="D179" s="205" t="s">
         <v>227</v>
       </c>
-      <c r="E179" s="313">
+      <c r="E179" s="311">
         <v>331644062</v>
       </c>
       <c r="F179" s="205" t="s">
@@ -47965,7 +47949,7 @@
       <c r="D180" s="205" t="s">
         <v>353</v>
       </c>
-      <c r="E180" s="313">
+      <c r="E180" s="311">
         <v>217415694</v>
       </c>
       <c r="F180" s="205" t="s">
@@ -48013,7 +47997,7 @@
       <c r="D181" s="205" t="s">
         <v>376</v>
       </c>
-      <c r="E181" s="313">
+      <c r="E181" s="311">
         <v>331109215</v>
       </c>
       <c r="F181" s="205" t="s">
@@ -48061,7 +48045,7 @@
       <c r="D182" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="E182" s="313">
+      <c r="E182" s="311">
         <v>333025971</v>
       </c>
       <c r="F182" s="205" t="s">
@@ -48109,7 +48093,7 @@
       <c r="D183" s="205" t="s">
         <v>96</v>
       </c>
-      <c r="E183" s="313">
+      <c r="E183" s="311">
         <v>332213669</v>
       </c>
       <c r="F183" s="205" t="s">
@@ -48157,7 +48141,7 @@
       <c r="D184" s="205" t="s">
         <v>519</v>
       </c>
-      <c r="E184" s="313">
+      <c r="E184" s="311">
         <v>331028837</v>
       </c>
       <c r="F184" s="205" t="s">
@@ -48175,7 +48159,7 @@
       <c r="J184" s="205" t="s">
         <v>860</v>
       </c>
-      <c r="K184" s="313">
+      <c r="K184" s="311">
         <v>10119675348</v>
       </c>
       <c r="L184" s="206" t="s">
@@ -48207,7 +48191,7 @@
       <c r="D185" s="205" t="s">
         <v>376</v>
       </c>
-      <c r="E185" s="313">
+      <c r="E185" s="311">
         <v>331033340</v>
       </c>
       <c r="F185" s="205" t="s">
@@ -48255,7 +48239,7 @@
       <c r="D186" s="205" t="s">
         <v>131</v>
       </c>
-      <c r="E186" s="313">
+      <c r="E186" s="311">
         <v>216993766</v>
       </c>
       <c r="F186" s="205" t="s">
@@ -48303,7 +48287,7 @@
       <c r="D187" s="205" t="s">
         <v>227</v>
       </c>
-      <c r="E187" s="313">
+      <c r="E187" s="311">
         <v>331695585</v>
       </c>
       <c r="F187" s="205" t="s">
@@ -48351,7 +48335,7 @@
       <c r="D188" s="205" t="s">
         <v>26</v>
       </c>
-      <c r="E188" s="313">
+      <c r="E188" s="311">
         <v>326552973</v>
       </c>
       <c r="F188" s="205" t="s">
@@ -48399,7 +48383,7 @@
       <c r="D189" s="205" t="s">
         <v>73</v>
       </c>
-      <c r="E189" s="313">
+      <c r="E189" s="311">
         <v>217405356</v>
       </c>
       <c r="F189" s="205" t="s">
@@ -48447,7 +48431,7 @@
       <c r="D190" s="205" t="s">
         <v>9</v>
       </c>
-      <c r="E190" s="313">
+      <c r="E190" s="311">
         <v>331720474</v>
       </c>
       <c r="F190" s="205" t="s">
@@ -48495,7 +48479,7 @@
       <c r="D191" s="205" t="s">
         <v>33</v>
       </c>
-      <c r="E191" s="313">
+      <c r="E191" s="311">
         <v>331127241</v>
       </c>
       <c r="F191" s="205" t="s">
@@ -48543,7 +48527,7 @@
       <c r="D192" s="205" t="s">
         <v>407</v>
       </c>
-      <c r="E192" s="313">
+      <c r="E192" s="311">
         <v>329615223</v>
       </c>
       <c r="F192" s="205" t="s">
@@ -48591,7 +48575,7 @@
       <c r="D193" s="205" t="s">
         <v>19</v>
       </c>
-      <c r="E193" s="313">
+      <c r="E193" s="311">
         <v>329097638</v>
       </c>
       <c r="F193" s="205" t="s">
@@ -48639,7 +48623,7 @@
       <c r="D194" s="205" t="s">
         <v>376</v>
       </c>
-      <c r="E194" s="313">
+      <c r="E194" s="311">
         <v>217671320</v>
       </c>
       <c r="F194" s="205" t="s">
@@ -48687,7 +48671,7 @@
       <c r="D195" s="205" t="s">
         <v>407</v>
       </c>
-      <c r="E195" s="313">
+      <c r="E195" s="311">
         <v>331751545</v>
       </c>
       <c r="F195" s="205" t="s">
@@ -48735,7 +48719,7 @@
       <c r="D196" s="205" t="s">
         <v>353</v>
       </c>
-      <c r="E196" s="313">
+      <c r="E196" s="311">
         <v>326598794</v>
       </c>
       <c r="F196" s="205" t="s">
@@ -48783,7 +48767,7 @@
       <c r="D197" s="205" t="s">
         <v>102</v>
       </c>
-      <c r="E197" s="313">
+      <c r="E197" s="311">
         <v>218022416</v>
       </c>
       <c r="F197" s="205" t="s">
@@ -48831,7 +48815,7 @@
       <c r="D198" s="205" t="s">
         <v>59</v>
       </c>
-      <c r="E198" s="313">
+      <c r="E198" s="311">
         <v>218094563</v>
       </c>
       <c r="F198" s="205" t="s">
@@ -48879,7 +48863,7 @@
       <c r="D199" s="205" t="s">
         <v>407</v>
       </c>
-      <c r="E199" s="313">
+      <c r="E199" s="311">
         <v>331468090</v>
       </c>
       <c r="F199" s="205" t="s">
@@ -48927,7 +48911,7 @@
       <c r="D200" s="205" t="s">
         <v>376</v>
       </c>
-      <c r="E200" s="313">
+      <c r="E200" s="311">
         <v>216413815</v>
       </c>
       <c r="F200" s="205" t="s">
@@ -48975,7 +48959,7 @@
       <c r="D201" s="205" t="s">
         <v>59</v>
       </c>
-      <c r="E201" s="313">
+      <c r="E201" s="311">
         <v>218301208</v>
       </c>
       <c r="F201" s="205" t="s">
@@ -49023,7 +49007,7 @@
       <c r="D202" s="205" t="s">
         <v>96</v>
       </c>
-      <c r="E202" s="313">
+      <c r="E202" s="311">
         <v>331961508</v>
       </c>
       <c r="F202" s="205" t="s">
@@ -49071,7 +49055,7 @@
       <c r="D203" s="205" t="s">
         <v>96</v>
       </c>
-      <c r="E203" s="313">
+      <c r="E203" s="311">
         <v>327767711</v>
       </c>
       <c r="F203" s="205" t="s">
@@ -49119,7 +49103,7 @@
       <c r="D204" s="205" t="s">
         <v>376</v>
       </c>
-      <c r="E204" s="313">
+      <c r="E204" s="311">
         <v>331026641</v>
       </c>
       <c r="F204" s="205" t="s">
@@ -49167,7 +49151,7 @@
       <c r="D205" s="205" t="s">
         <v>96</v>
       </c>
-      <c r="E205" s="313">
+      <c r="E205" s="311">
         <v>333133106</v>
       </c>
       <c r="F205" s="205" t="s">
@@ -49215,7 +49199,7 @@
       <c r="D206" s="205" t="s">
         <v>59</v>
       </c>
-      <c r="E206" s="313">
+      <c r="E206" s="311">
         <v>217567833</v>
       </c>
       <c r="F206" s="205" t="s">
@@ -49263,7 +49247,7 @@
       <c r="D207" s="205" t="s">
         <v>96</v>
       </c>
-      <c r="E207" s="313">
+      <c r="E207" s="311">
         <v>217600840</v>
       </c>
       <c r="F207" s="205" t="s">
@@ -49311,7 +49295,7 @@
       <c r="D208" s="217" t="s">
         <v>26</v>
       </c>
-      <c r="E208" s="314">
+      <c r="E208" s="312">
         <v>331593624</v>
       </c>
       <c r="F208" s="217" t="s">
@@ -49329,8 +49313,8 @@
       <c r="J208" s="217" t="s">
         <v>30</v>
       </c>
-      <c r="K208" s="336"/>
-      <c r="L208" s="336" t="s">
+      <c r="K208" s="333"/>
+      <c r="L208" s="333" t="s">
         <v>31</v>
       </c>
       <c r="M208" s="218" t="s">
@@ -49346,7 +49330,7 @@
         <v>0.60416666666666663</v>
       </c>
     </row>
-    <row r="209" spans="1:16" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:16" ht="36.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A209" s="157" t="s">
         <v>1284</v>
       </c>
@@ -49377,7 +49361,7 @@
       <c r="J209" s="4" t="s">
         <v>1293</v>
       </c>
-      <c r="K209" s="326" t="s">
+      <c r="K209" s="324" t="s">
         <v>1294</v>
       </c>
       <c r="L209" s="285" t="s">
@@ -49386,7 +49370,7 @@
       <c r="M209" s="285" t="s">
         <v>5</v>
       </c>
-      <c r="N209" s="359" t="s">
+      <c r="N209" s="356" t="s">
         <v>1285</v>
       </c>
       <c r="O209" s="285" t="s">
@@ -49409,7 +49393,7 @@
       <c r="D210" s="223" t="s">
         <v>59</v>
       </c>
-      <c r="E210" s="315">
+      <c r="E210" s="313">
         <v>330955790</v>
       </c>
       <c r="F210" s="223" t="s">
@@ -49427,8 +49411,8 @@
       <c r="J210" s="223" t="s">
         <v>1136</v>
       </c>
-      <c r="K210" s="337"/>
-      <c r="L210" s="337" t="s">
+      <c r="K210" s="334"/>
+      <c r="L210" s="334" t="s">
         <v>1137</v>
       </c>
       <c r="M210" s="224" t="s">
@@ -49457,7 +49441,7 @@
       <c r="D211" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="E211" s="302">
+      <c r="E211" s="300">
         <v>216172148</v>
       </c>
       <c r="F211" s="122" t="s">
@@ -49475,8 +49459,8 @@
       <c r="J211" s="122" t="s">
         <v>889</v>
       </c>
-      <c r="K211" s="338"/>
-      <c r="L211" s="338" t="s">
+      <c r="K211" s="335"/>
+      <c r="L211" s="335" t="s">
         <v>890</v>
       </c>
       <c r="M211" s="123" t="s">
@@ -49505,7 +49489,7 @@
       <c r="D212" s="122" t="s">
         <v>227</v>
       </c>
-      <c r="E212" s="302">
+      <c r="E212" s="300">
         <v>216150953</v>
       </c>
       <c r="F212" s="122" t="s">
@@ -49523,8 +49507,8 @@
       <c r="J212" s="122" t="s">
         <v>268</v>
       </c>
-      <c r="K212" s="338"/>
-      <c r="L212" s="338" t="s">
+      <c r="K212" s="335"/>
+      <c r="L212" s="335" t="s">
         <v>269</v>
       </c>
       <c r="M212" s="123" t="s">
@@ -49553,7 +49537,7 @@
       <c r="D213" s="122" t="s">
         <v>73</v>
       </c>
-      <c r="E213" s="302">
+      <c r="E213" s="300">
         <v>327792347</v>
       </c>
       <c r="F213" s="122" t="s">
@@ -49571,8 +49555,8 @@
       <c r="J213" s="122" t="s">
         <v>912</v>
       </c>
-      <c r="K213" s="338"/>
-      <c r="L213" s="338" t="s">
+      <c r="K213" s="335"/>
+      <c r="L213" s="335" t="s">
         <v>913</v>
       </c>
       <c r="M213" s="123" t="s">
@@ -49601,7 +49585,7 @@
       <c r="D214" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="E214" s="302">
+      <c r="E214" s="300">
         <v>216853960</v>
       </c>
       <c r="F214" s="122" t="s">
@@ -49619,8 +49603,8 @@
       <c r="J214" s="122" t="s">
         <v>1231</v>
       </c>
-      <c r="K214" s="338"/>
-      <c r="L214" s="338" t="s">
+      <c r="K214" s="335"/>
+      <c r="L214" s="335" t="s">
         <v>1232</v>
       </c>
       <c r="M214" s="123" t="s">
@@ -49649,7 +49633,7 @@
       <c r="D215" s="122" t="s">
         <v>19</v>
       </c>
-      <c r="E215" s="302">
+      <c r="E215" s="300">
         <v>216643064</v>
       </c>
       <c r="F215" s="122" t="s">
@@ -49667,8 +49651,8 @@
       <c r="J215" s="122" t="s">
         <v>669</v>
       </c>
-      <c r="K215" s="338"/>
-      <c r="L215" s="338" t="s">
+      <c r="K215" s="335"/>
+      <c r="L215" s="335" t="s">
         <v>670</v>
       </c>
       <c r="M215" s="123" t="s">
@@ -49697,7 +49681,7 @@
       <c r="D216" s="122" t="s">
         <v>59</v>
       </c>
-      <c r="E216" s="302">
+      <c r="E216" s="300">
         <v>331621003</v>
       </c>
       <c r="F216" s="122" t="s">
@@ -49715,8 +49699,8 @@
       <c r="J216" s="122" t="s">
         <v>1234</v>
       </c>
-      <c r="K216" s="338"/>
-      <c r="L216" s="338" t="s">
+      <c r="K216" s="335"/>
+      <c r="L216" s="335" t="s">
         <v>1235</v>
       </c>
       <c r="M216" s="123" t="s">
@@ -49745,7 +49729,7 @@
       <c r="D217" s="122" t="s">
         <v>73</v>
       </c>
-      <c r="E217" s="302">
+      <c r="E217" s="300">
         <v>328318902</v>
       </c>
       <c r="F217" s="122" t="s">
@@ -49763,8 +49747,8 @@
       <c r="J217" s="122" t="s">
         <v>813</v>
       </c>
-      <c r="K217" s="338"/>
-      <c r="L217" s="338" t="s">
+      <c r="K217" s="335"/>
+      <c r="L217" s="335" t="s">
         <v>814</v>
       </c>
       <c r="M217" s="123" t="s">
@@ -49793,7 +49777,7 @@
       <c r="D218" s="122" t="s">
         <v>227</v>
       </c>
-      <c r="E218" s="302">
+      <c r="E218" s="300">
         <v>326756822</v>
       </c>
       <c r="F218" s="122" t="s">
@@ -49811,8 +49795,8 @@
       <c r="J218" s="122" t="s">
         <v>781</v>
       </c>
-      <c r="K218" s="338"/>
-      <c r="L218" s="338" t="s">
+      <c r="K218" s="335"/>
+      <c r="L218" s="335" t="s">
         <v>782</v>
       </c>
       <c r="M218" s="123" t="s">
@@ -49841,7 +49825,7 @@
       <c r="D219" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="E219" s="302">
+      <c r="E219" s="300">
         <v>330810151</v>
       </c>
       <c r="F219" s="122" t="s">
@@ -49859,8 +49843,8 @@
       <c r="J219" s="122" t="s">
         <v>388</v>
       </c>
-      <c r="K219" s="338"/>
-      <c r="L219" s="338" t="s">
+      <c r="K219" s="335"/>
+      <c r="L219" s="335" t="s">
         <v>389</v>
       </c>
       <c r="M219" s="123" t="s">
@@ -49889,7 +49873,7 @@
       <c r="D220" s="122" t="s">
         <v>9</v>
       </c>
-      <c r="E220" s="302">
+      <c r="E220" s="300">
         <v>330888801</v>
       </c>
       <c r="F220" s="122" t="s">
@@ -49907,8 +49891,8 @@
       <c r="J220" s="122" t="s">
         <v>735</v>
       </c>
-      <c r="K220" s="338"/>
-      <c r="L220" s="338" t="s">
+      <c r="K220" s="335"/>
+      <c r="L220" s="335" t="s">
         <v>736</v>
       </c>
       <c r="M220" s="123" t="s">
@@ -49937,7 +49921,7 @@
       <c r="D221" s="122" t="s">
         <v>9</v>
       </c>
-      <c r="E221" s="302">
+      <c r="E221" s="300">
         <v>217304575</v>
       </c>
       <c r="F221" s="122" t="s">
@@ -49955,8 +49939,8 @@
       <c r="J221" s="122" t="s">
         <v>755</v>
       </c>
-      <c r="K221" s="338"/>
-      <c r="L221" s="338" t="s">
+      <c r="K221" s="335"/>
+      <c r="L221" s="335" t="s">
         <v>756</v>
       </c>
       <c r="M221" s="123" t="s">
@@ -49985,7 +49969,7 @@
       <c r="D222" s="122" t="s">
         <v>407</v>
       </c>
-      <c r="E222" s="302">
+      <c r="E222" s="300">
         <v>215889619</v>
       </c>
       <c r="F222" s="122" t="s">
@@ -50003,8 +49987,8 @@
       <c r="J222" s="122" t="s">
         <v>661</v>
       </c>
-      <c r="K222" s="338"/>
-      <c r="L222" s="338" t="s">
+      <c r="K222" s="335"/>
+      <c r="L222" s="335" t="s">
         <v>662</v>
       </c>
       <c r="M222" s="123" t="s">
@@ -50033,7 +50017,7 @@
       <c r="D223" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="E223" s="302">
+      <c r="E223" s="300">
         <v>216290825</v>
       </c>
       <c r="F223" s="122" t="s">
@@ -50051,8 +50035,8 @@
       <c r="J223" s="122" t="s">
         <v>331</v>
       </c>
-      <c r="K223" s="338"/>
-      <c r="L223" s="338" t="s">
+      <c r="K223" s="335"/>
+      <c r="L223" s="335" t="s">
         <v>332</v>
       </c>
       <c r="M223" s="123" t="s">
@@ -50081,7 +50065,7 @@
       <c r="D224" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="E224" s="302">
+      <c r="E224" s="300">
         <v>331776948</v>
       </c>
       <c r="F224" s="122" t="s">
@@ -50099,8 +50083,8 @@
       <c r="J224" s="122" t="s">
         <v>419</v>
       </c>
-      <c r="K224" s="338"/>
-      <c r="L224" s="338" t="s">
+      <c r="K224" s="335"/>
+      <c r="L224" s="335" t="s">
         <v>420</v>
       </c>
       <c r="M224" s="123" t="s">
@@ -50130,7 +50114,7 @@
       <c r="D225" s="127" t="s">
         <v>59</v>
       </c>
-      <c r="E225" s="316">
+      <c r="E225" s="314">
         <v>216787879</v>
       </c>
       <c r="F225" s="127" t="s">
@@ -50148,8 +50132,8 @@
       <c r="J225" s="127" t="s">
         <v>601</v>
       </c>
-      <c r="K225" s="339"/>
-      <c r="L225" s="339" t="s">
+      <c r="K225" s="336"/>
+      <c r="L225" s="336" t="s">
         <v>602</v>
       </c>
       <c r="M225" s="128" t="s">
@@ -50165,7 +50149,7 @@
         <v>0.65625</v>
       </c>
     </row>
-    <row r="226" spans="1:16" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:16" ht="36.6" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A226" s="157" t="s">
         <v>1284</v>
       </c>
@@ -50196,7 +50180,7 @@
       <c r="J226" s="4" t="s">
         <v>1293</v>
       </c>
-      <c r="K226" s="326" t="s">
+      <c r="K226" s="324" t="s">
         <v>1294</v>
       </c>
       <c r="L226" s="285" t="s">
@@ -50205,7 +50189,7 @@
       <c r="M226" s="285" t="s">
         <v>5</v>
       </c>
-      <c r="N226" s="359" t="s">
+      <c r="N226" s="356" t="s">
         <v>1285</v>
       </c>
       <c r="O226" s="285" t="s">
@@ -50228,7 +50212,7 @@
       <c r="D227" s="270" t="s">
         <v>73</v>
       </c>
-      <c r="E227" s="317">
+      <c r="E227" s="315">
         <v>329098867</v>
       </c>
       <c r="F227" s="270" t="s">
@@ -50246,8 +50230,8 @@
       <c r="J227" s="270" t="s">
         <v>866</v>
       </c>
-      <c r="K227" s="340"/>
-      <c r="L227" s="340" t="s">
+      <c r="K227" s="337"/>
+      <c r="L227" s="337" t="s">
         <v>867</v>
       </c>
       <c r="M227" s="271" t="s">
@@ -50276,7 +50260,7 @@
       <c r="D228" s="262" t="s">
         <v>19</v>
       </c>
-      <c r="E228" s="318">
+      <c r="E228" s="316">
         <v>331936021</v>
       </c>
       <c r="F228" s="262" t="s">
@@ -50294,8 +50278,8 @@
       <c r="J228" s="262" t="s">
         <v>56</v>
       </c>
-      <c r="K228" s="341"/>
-      <c r="L228" s="341" t="s">
+      <c r="K228" s="338"/>
+      <c r="L228" s="338" t="s">
         <v>57</v>
       </c>
       <c r="M228" s="263" t="s">
@@ -50324,7 +50308,7 @@
       <c r="D229" s="262" t="s">
         <v>73</v>
       </c>
-      <c r="E229" s="318">
+      <c r="E229" s="316">
         <v>331212951</v>
       </c>
       <c r="F229" s="262" t="s">
@@ -50342,8 +50326,8 @@
       <c r="J229" s="262" t="s">
         <v>487</v>
       </c>
-      <c r="K229" s="341"/>
-      <c r="L229" s="341" t="s">
+      <c r="K229" s="338"/>
+      <c r="L229" s="338" t="s">
         <v>488</v>
       </c>
       <c r="M229" s="263" t="s">
@@ -50372,7 +50356,7 @@
       <c r="D230" s="262" t="s">
         <v>270</v>
       </c>
-      <c r="E230" s="318">
+      <c r="E230" s="316">
         <v>217794437</v>
       </c>
       <c r="F230" s="262" t="s">
@@ -50390,8 +50374,8 @@
       <c r="J230" s="262" t="s">
         <v>1181</v>
       </c>
-      <c r="K230" s="341"/>
-      <c r="L230" s="341" t="s">
+      <c r="K230" s="338"/>
+      <c r="L230" s="338" t="s">
         <v>1213</v>
       </c>
       <c r="M230" s="263" t="s">
@@ -50420,7 +50404,7 @@
       <c r="D231" s="262" t="s">
         <v>19</v>
       </c>
-      <c r="E231" s="318">
+      <c r="E231" s="316">
         <v>331949131</v>
       </c>
       <c r="F231" s="262" t="s">
@@ -50438,8 +50422,8 @@
       <c r="J231" s="262" t="s">
         <v>23</v>
       </c>
-      <c r="K231" s="341"/>
-      <c r="L231" s="341" t="s">
+      <c r="K231" s="338"/>
+      <c r="L231" s="338" t="s">
         <v>24</v>
       </c>
       <c r="M231" s="263" t="s">
@@ -50468,7 +50452,7 @@
       <c r="D232" s="262" t="s">
         <v>73</v>
       </c>
-      <c r="E232" s="318">
+      <c r="E232" s="316">
         <v>217441526</v>
       </c>
       <c r="F232" s="262" t="s">
@@ -50486,8 +50470,8 @@
       <c r="J232" s="262" t="s">
         <v>393</v>
       </c>
-      <c r="K232" s="341"/>
-      <c r="L232" s="341" t="s">
+      <c r="K232" s="338"/>
+      <c r="L232" s="338" t="s">
         <v>394</v>
       </c>
       <c r="M232" s="263" t="s">
@@ -50516,7 +50500,7 @@
       <c r="D233" s="262" t="s">
         <v>407</v>
       </c>
-      <c r="E233" s="318">
+      <c r="E233" s="316">
         <v>333036499</v>
       </c>
       <c r="F233" s="262" t="s">
@@ -50534,8 +50518,8 @@
       <c r="J233" s="262" t="s">
         <v>786</v>
       </c>
-      <c r="K233" s="341"/>
-      <c r="L233" s="341" t="s">
+      <c r="K233" s="338"/>
+      <c r="L233" s="338" t="s">
         <v>789</v>
       </c>
       <c r="M233" s="263" t="s">
@@ -50564,7 +50548,7 @@
       <c r="D234" s="262" t="s">
         <v>73</v>
       </c>
-      <c r="E234" s="318">
+      <c r="E234" s="316">
         <v>331258723</v>
       </c>
       <c r="F234" s="262" t="s">
@@ -50582,8 +50566,8 @@
       <c r="J234" s="262" t="s">
         <v>300</v>
       </c>
-      <c r="K234" s="341"/>
-      <c r="L234" s="341" t="s">
+      <c r="K234" s="338"/>
+      <c r="L234" s="338" t="s">
         <v>301</v>
       </c>
       <c r="M234" s="263" t="s">
@@ -50612,7 +50596,7 @@
       <c r="D235" s="262" t="s">
         <v>19</v>
       </c>
-      <c r="E235" s="318">
+      <c r="E235" s="316">
         <v>331945170</v>
       </c>
       <c r="F235" s="262" t="s">
@@ -50630,8 +50614,8 @@
       <c r="J235" s="262" t="s">
         <v>56</v>
       </c>
-      <c r="K235" s="341"/>
-      <c r="L235" s="341" t="s">
+      <c r="K235" s="338"/>
+      <c r="L235" s="338" t="s">
         <v>645</v>
       </c>
       <c r="M235" s="263" t="s">
@@ -50660,7 +50644,7 @@
       <c r="D236" s="262" t="s">
         <v>353</v>
       </c>
-      <c r="E236" s="318">
+      <c r="E236" s="316">
         <v>217943950</v>
       </c>
       <c r="F236" s="262" t="s">
@@ -50678,8 +50662,8 @@
       <c r="J236" s="262" t="s">
         <v>983</v>
       </c>
-      <c r="K236" s="341"/>
-      <c r="L236" s="341" t="s">
+      <c r="K236" s="338"/>
+      <c r="L236" s="338" t="s">
         <v>984</v>
       </c>
       <c r="M236" s="263" t="s">
@@ -50708,7 +50692,7 @@
       <c r="D237" s="262" t="s">
         <v>190</v>
       </c>
-      <c r="E237" s="318">
+      <c r="E237" s="316">
         <v>331522185</v>
       </c>
       <c r="F237" s="262" t="s">
@@ -50726,8 +50710,8 @@
       <c r="J237" s="262" t="s">
         <v>464</v>
       </c>
-      <c r="K237" s="341"/>
-      <c r="L237" s="341" t="s">
+      <c r="K237" s="338"/>
+      <c r="L237" s="338" t="s">
         <v>465</v>
       </c>
       <c r="M237" s="263" t="s">
@@ -50756,7 +50740,7 @@
       <c r="D238" s="262" t="s">
         <v>270</v>
       </c>
-      <c r="E238" s="318">
+      <c r="E238" s="316">
         <v>333008332</v>
       </c>
       <c r="F238" s="262" t="s">
@@ -50774,8 +50758,8 @@
       <c r="J238" s="262" t="s">
         <v>1033</v>
       </c>
-      <c r="K238" s="341"/>
-      <c r="L238" s="341" t="s">
+      <c r="K238" s="338"/>
+      <c r="L238" s="338" t="s">
         <v>1034</v>
       </c>
       <c r="M238" s="263" t="s">
@@ -50804,7 +50788,7 @@
       <c r="D239" s="262" t="s">
         <v>370</v>
       </c>
-      <c r="E239" s="318">
+      <c r="E239" s="316">
         <v>331497537</v>
       </c>
       <c r="F239" s="262" t="s">
@@ -50822,8 +50806,8 @@
       <c r="J239" s="262" t="s">
         <v>1026</v>
       </c>
-      <c r="K239" s="341"/>
-      <c r="L239" s="341" t="s">
+      <c r="K239" s="338"/>
+      <c r="L239" s="338" t="s">
         <v>1027</v>
       </c>
       <c r="M239" s="263" t="s">
@@ -50852,7 +50836,7 @@
       <c r="D240" s="262" t="s">
         <v>73</v>
       </c>
-      <c r="E240" s="318">
+      <c r="E240" s="316">
         <v>331252528</v>
       </c>
       <c r="F240" s="262" t="s">
@@ -50870,8 +50854,8 @@
       <c r="J240" s="262" t="s">
         <v>471</v>
       </c>
-      <c r="K240" s="341"/>
-      <c r="L240" s="341" t="s">
+      <c r="K240" s="338"/>
+      <c r="L240" s="338" t="s">
         <v>472</v>
       </c>
       <c r="M240" s="263" t="s">
@@ -50900,7 +50884,7 @@
       <c r="D241" s="262" t="s">
         <v>59</v>
       </c>
-      <c r="E241" s="318">
+      <c r="E241" s="316">
         <v>218086700</v>
       </c>
       <c r="F241" s="262" t="s">
@@ -50918,8 +50902,8 @@
       <c r="J241" s="262" t="s">
         <v>89</v>
       </c>
-      <c r="K241" s="341"/>
-      <c r="L241" s="341" t="s">
+      <c r="K241" s="338"/>
+      <c r="L241" s="338" t="s">
         <v>90</v>
       </c>
       <c r="M241" s="263" t="s">
@@ -50948,7 +50932,7 @@
       <c r="D242" s="262" t="s">
         <v>19</v>
       </c>
-      <c r="E242" s="318">
+      <c r="E242" s="316">
         <v>216187849</v>
       </c>
       <c r="F242" s="262" t="s">
@@ -50966,8 +50950,8 @@
       <c r="J242" s="262" t="s">
         <v>482</v>
       </c>
-      <c r="K242" s="341"/>
-      <c r="L242" s="341" t="s">
+      <c r="K242" s="338"/>
+      <c r="L242" s="338" t="s">
         <v>483</v>
       </c>
       <c r="M242" s="263" t="s">
@@ -50996,7 +50980,7 @@
       <c r="D243" s="262" t="s">
         <v>353</v>
       </c>
-      <c r="E243" s="318">
+      <c r="E243" s="316">
         <v>333023778</v>
       </c>
       <c r="F243" s="262" t="s">
@@ -51014,8 +50998,8 @@
       <c r="J243" s="262" t="s">
         <v>980</v>
       </c>
-      <c r="K243" s="341"/>
-      <c r="L243" s="341" t="s">
+      <c r="K243" s="338"/>
+      <c r="L243" s="338" t="s">
         <v>981</v>
       </c>
       <c r="M243" s="263" t="s">
@@ -51044,7 +51028,7 @@
       <c r="D244" s="262" t="s">
         <v>270</v>
       </c>
-      <c r="E244" s="318">
+      <c r="E244" s="316">
         <v>217583830</v>
       </c>
       <c r="F244" s="262" t="s">
@@ -51062,8 +51046,8 @@
       <c r="J244" s="262" t="s">
         <v>1042</v>
       </c>
-      <c r="K244" s="341"/>
-      <c r="L244" s="341" t="s">
+      <c r="K244" s="338"/>
+      <c r="L244" s="338" t="s">
         <v>1043</v>
       </c>
       <c r="M244" s="263" t="s">
@@ -51092,7 +51076,7 @@
       <c r="D245" s="262" t="s">
         <v>270</v>
       </c>
-      <c r="E245" s="318">
+      <c r="E245" s="316">
         <v>333595445</v>
       </c>
       <c r="F245" s="262" t="s">
@@ -51110,8 +51094,8 @@
       <c r="J245" s="262" t="s">
         <v>274</v>
       </c>
-      <c r="K245" s="341"/>
-      <c r="L245" s="341" t="s">
+      <c r="K245" s="338"/>
+      <c r="L245" s="338" t="s">
         <v>275</v>
       </c>
       <c r="M245" s="263" t="s">
@@ -51140,7 +51124,7 @@
       <c r="D246" s="262" t="s">
         <v>19</v>
       </c>
-      <c r="E246" s="318">
+      <c r="E246" s="316">
         <v>331175372</v>
       </c>
       <c r="F246" s="262" t="s">
@@ -51158,8 +51142,8 @@
       <c r="J246" s="262" t="s">
         <v>404</v>
       </c>
-      <c r="K246" s="341"/>
-      <c r="L246" s="341" t="s">
+      <c r="K246" s="338"/>
+      <c r="L246" s="338" t="s">
         <v>405</v>
       </c>
       <c r="M246" s="263" t="s">
@@ -51188,7 +51172,7 @@
       <c r="D247" s="262" t="s">
         <v>26</v>
       </c>
-      <c r="E247" s="318">
+      <c r="E247" s="316">
         <v>334332590</v>
       </c>
       <c r="F247" s="262" t="s">
@@ -51206,8 +51190,8 @@
       <c r="J247" s="262" t="s">
         <v>613</v>
       </c>
-      <c r="K247" s="341"/>
-      <c r="L247" s="341" t="s">
+      <c r="K247" s="338"/>
+      <c r="L247" s="338" t="s">
         <v>614</v>
       </c>
       <c r="M247" s="263" t="s">
@@ -51236,7 +51220,7 @@
       <c r="D248" s="262" t="s">
         <v>353</v>
       </c>
-      <c r="E248" s="318">
+      <c r="E248" s="316">
         <v>333135655</v>
       </c>
       <c r="F248" s="262" t="s">
@@ -51254,8 +51238,8 @@
       <c r="J248" s="262" t="s">
         <v>921</v>
       </c>
-      <c r="K248" s="341"/>
-      <c r="L248" s="341" t="s">
+      <c r="K248" s="338"/>
+      <c r="L248" s="338" t="s">
         <v>922</v>
       </c>
       <c r="M248" s="263" t="s">
@@ -51284,7 +51268,7 @@
       <c r="D249" s="262" t="s">
         <v>19</v>
       </c>
-      <c r="E249" s="318">
+      <c r="E249" s="316">
         <v>216652552</v>
       </c>
       <c r="F249" s="262" t="s">
@@ -51302,8 +51286,8 @@
       <c r="J249" s="262" t="s">
         <v>255</v>
       </c>
-      <c r="K249" s="341"/>
-      <c r="L249" s="341" t="s">
+      <c r="K249" s="338"/>
+      <c r="L249" s="338" t="s">
         <v>256</v>
       </c>
       <c r="M249" s="263" t="s">
@@ -51332,7 +51316,7 @@
       <c r="D250" s="262" t="s">
         <v>26</v>
       </c>
-      <c r="E250" s="318">
+      <c r="E250" s="316">
         <v>333599389</v>
       </c>
       <c r="F250" s="262" t="s">
@@ -51350,8 +51334,8 @@
       <c r="J250" s="262" t="s">
         <v>616</v>
       </c>
-      <c r="K250" s="341"/>
-      <c r="L250" s="341" t="s">
+      <c r="K250" s="338"/>
+      <c r="L250" s="338" t="s">
         <v>364</v>
       </c>
       <c r="M250" s="263" t="s">
@@ -51380,7 +51364,7 @@
       <c r="D251" s="262" t="s">
         <v>73</v>
       </c>
-      <c r="E251" s="318">
+      <c r="E251" s="316">
         <v>331255836</v>
       </c>
       <c r="F251" s="262" t="s">
@@ -51398,8 +51382,8 @@
       <c r="J251" s="262" t="s">
         <v>718</v>
       </c>
-      <c r="K251" s="341"/>
-      <c r="L251" s="341" t="s">
+      <c r="K251" s="338"/>
+      <c r="L251" s="338" t="s">
         <v>719</v>
       </c>
       <c r="M251" s="263" t="s">
@@ -51428,7 +51412,7 @@
       <c r="D252" s="262" t="s">
         <v>59</v>
       </c>
-      <c r="E252" s="318">
+      <c r="E252" s="316">
         <v>218026797</v>
       </c>
       <c r="F252" s="262" t="s">
@@ -51446,8 +51430,8 @@
       <c r="J252" s="262" t="s">
         <v>1019</v>
       </c>
-      <c r="K252" s="341"/>
-      <c r="L252" s="341" t="s">
+      <c r="K252" s="338"/>
+      <c r="L252" s="338" t="s">
         <v>1020</v>
       </c>
       <c r="M252" s="263" t="s">
@@ -51476,7 +51460,7 @@
       <c r="D253" s="281" t="s">
         <v>270</v>
       </c>
-      <c r="E253" s="319">
+      <c r="E253" s="317">
         <v>331478305</v>
       </c>
       <c r="F253" s="281" t="s">
@@ -51494,8 +51478,8 @@
       <c r="J253" s="281" t="s">
         <v>1131</v>
       </c>
-      <c r="K253" s="342"/>
-      <c r="L253" s="342" t="s">
+      <c r="K253" s="339"/>
+      <c r="L253" s="339" t="s">
         <v>1132</v>
       </c>
       <c r="M253" s="282" t="s">
@@ -51524,7 +51508,7 @@
       <c r="D254" s="275" t="s">
         <v>73</v>
       </c>
-      <c r="E254" s="320">
+      <c r="E254" s="318">
         <v>332124130</v>
       </c>
       <c r="F254" s="275" t="s">
@@ -51542,8 +51526,8 @@
       <c r="J254" s="275" t="s">
         <v>83</v>
       </c>
-      <c r="K254" s="343"/>
-      <c r="L254" s="343" t="s">
+      <c r="K254" s="340"/>
+      <c r="L254" s="340" t="s">
         <v>85</v>
       </c>
       <c r="M254" s="276" t="s">
@@ -51572,7 +51556,7 @@
       <c r="D255" s="256" t="s">
         <v>353</v>
       </c>
-      <c r="E255" s="321">
+      <c r="E255" s="319">
         <v>333692929</v>
       </c>
       <c r="F255" s="256" t="s">
@@ -51590,8 +51574,8 @@
       <c r="J255" s="256" t="s">
         <v>963</v>
       </c>
-      <c r="K255" s="344"/>
-      <c r="L255" s="344" t="s">
+      <c r="K255" s="341"/>
+      <c r="L255" s="341" t="s">
         <v>405</v>
       </c>
       <c r="M255" s="257" t="s">
@@ -51607,53 +51591,53 @@
         <v>0.69791666666666663</v>
       </c>
     </row>
-    <row r="256" spans="1:16" ht="35.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A256" s="354" t="s">
+    <row r="256" spans="1:16" ht="36.6" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A256" s="351" t="s">
         <v>1284</v>
       </c>
-      <c r="B256" s="355" t="s">
+      <c r="B256" s="352" t="s">
         <v>1290</v>
       </c>
-      <c r="C256" s="355" t="s">
+      <c r="C256" s="352" t="s">
         <v>0</v>
       </c>
-      <c r="D256" s="356" t="s">
+      <c r="D256" s="353" t="s">
         <v>1</v>
       </c>
-      <c r="E256" s="355" t="s">
+      <c r="E256" s="352" t="s">
         <v>1291</v>
       </c>
-      <c r="F256" s="356" t="s">
+      <c r="F256" s="353" t="s">
         <v>2</v>
       </c>
-      <c r="G256" s="356" t="s">
+      <c r="G256" s="353" t="s">
         <v>3</v>
       </c>
-      <c r="H256" s="356" t="s">
+      <c r="H256" s="353" t="s">
         <v>4</v>
       </c>
-      <c r="I256" s="356" t="s">
+      <c r="I256" s="353" t="s">
         <v>1292</v>
       </c>
-      <c r="J256" s="356" t="s">
+      <c r="J256" s="353" t="s">
         <v>1293</v>
       </c>
-      <c r="K256" s="357" t="s">
+      <c r="K256" s="354" t="s">
         <v>1294</v>
       </c>
-      <c r="L256" s="355" t="s">
+      <c r="L256" s="352" t="s">
         <v>6</v>
       </c>
-      <c r="M256" s="355" t="s">
+      <c r="M256" s="352" t="s">
         <v>5</v>
       </c>
-      <c r="N256" s="360" t="s">
+      <c r="N256" s="357" t="s">
         <v>1285</v>
       </c>
-      <c r="O256" s="355" t="s">
+      <c r="O256" s="352" t="s">
         <v>1286</v>
       </c>
-      <c r="P256" s="358" t="s">
+      <c r="P256" s="355" t="s">
         <v>1287</v>
       </c>
     </row>
@@ -51670,7 +51654,7 @@
       <c r="D257" s="232" t="s">
         <v>276</v>
       </c>
-      <c r="E257" s="322">
+      <c r="E257" s="320">
         <v>219517281</v>
       </c>
       <c r="F257" s="232" t="s">
@@ -51688,8 +51672,8 @@
       <c r="J257" s="232" t="s">
         <v>539</v>
       </c>
-      <c r="K257" s="345"/>
-      <c r="L257" s="345" t="s">
+      <c r="K257" s="342"/>
+      <c r="L257" s="342" t="s">
         <v>540</v>
       </c>
       <c r="M257" s="233" t="s">
@@ -51718,7 +51702,7 @@
       <c r="D258" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="E258" s="306">
+      <c r="E258" s="304">
         <v>334466950</v>
       </c>
       <c r="F258" s="37" t="s">
@@ -51766,7 +51750,7 @@
       <c r="D259" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="E259" s="306">
+      <c r="E259" s="304">
         <v>219047966</v>
       </c>
       <c r="F259" s="37" t="s">
@@ -51814,7 +51798,7 @@
       <c r="D260" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="E260" s="306">
+      <c r="E260" s="304">
         <v>220179394</v>
       </c>
       <c r="F260" s="37" t="s">
@@ -51862,7 +51846,7 @@
       <c r="D261" s="37" t="s">
         <v>429</v>
       </c>
-      <c r="E261" s="306">
+      <c r="E261" s="304">
         <v>334391158</v>
       </c>
       <c r="F261" s="37" t="s">
@@ -51910,7 +51894,7 @@
       <c r="D262" s="37" t="s">
         <v>429</v>
       </c>
-      <c r="E262" s="306">
+      <c r="E262" s="304">
         <v>334391166</v>
       </c>
       <c r="F262" s="37" t="s">
@@ -51958,7 +51942,7 @@
       <c r="D263" s="37" t="s">
         <v>407</v>
       </c>
-      <c r="E263" s="306">
+      <c r="E263" s="304">
         <v>334665676</v>
       </c>
       <c r="F263" s="37" t="s">
@@ -52006,7 +51990,7 @@
       <c r="D264" s="37" t="s">
         <v>33</v>
       </c>
-      <c r="E264" s="306">
+      <c r="E264" s="304">
         <v>219487022</v>
       </c>
       <c r="F264" s="37" t="s">
@@ -52054,7 +52038,7 @@
       <c r="D265" s="37" t="s">
         <v>407</v>
       </c>
-      <c r="E265" s="306">
+      <c r="E265" s="304">
         <v>334933611</v>
       </c>
       <c r="F265" s="37" t="s">
@@ -52102,7 +52086,7 @@
       <c r="D266" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E266" s="306">
+      <c r="E266" s="304">
         <v>219213824</v>
       </c>
       <c r="F266" s="37" t="s">
@@ -52150,7 +52134,7 @@
       <c r="D267" s="37" t="s">
         <v>429</v>
       </c>
-      <c r="E267" s="306">
+      <c r="E267" s="304">
         <v>334837218</v>
       </c>
       <c r="F267" s="37" t="s">
@@ -52198,7 +52182,7 @@
       <c r="D268" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="E268" s="306">
+      <c r="E268" s="304">
         <v>219800315</v>
       </c>
       <c r="F268" s="37" t="s">
@@ -52246,7 +52230,7 @@
       <c r="D269" s="37" t="s">
         <v>376</v>
       </c>
-      <c r="E269" s="306">
+      <c r="E269" s="304">
         <v>334584794</v>
       </c>
       <c r="F269" s="37" t="s">
@@ -52294,7 +52278,7 @@
       <c r="D270" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="E270" s="306">
+      <c r="E270" s="304">
         <v>219779238</v>
       </c>
       <c r="F270" s="37" t="s">
@@ -52342,7 +52326,7 @@
       <c r="D271" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="E271" s="306">
+      <c r="E271" s="304">
         <v>219417995</v>
       </c>
       <c r="F271" s="37" t="s">
@@ -52390,7 +52374,7 @@
       <c r="D272" s="37" t="s">
         <v>407</v>
       </c>
-      <c r="E272" s="306">
+      <c r="E272" s="304">
         <v>219912367</v>
       </c>
       <c r="F272" s="37" t="s">
@@ -52438,7 +52422,7 @@
       <c r="D273" s="37" t="s">
         <v>407</v>
       </c>
-      <c r="E273" s="306">
+      <c r="E273" s="304">
         <v>220030241</v>
       </c>
       <c r="F273" s="37" t="s">
@@ -52486,7 +52470,7 @@
       <c r="D274" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="E274" s="306">
+      <c r="E274" s="304">
         <v>334705647</v>
       </c>
       <c r="F274" s="37" t="s">
@@ -52534,7 +52518,7 @@
       <c r="D275" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="E275" s="306">
+      <c r="E275" s="304">
         <v>333609691</v>
       </c>
       <c r="F275" s="37" t="s">
@@ -52582,7 +52566,7 @@
       <c r="D276" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="E276" s="306">
+      <c r="E276" s="304">
         <v>334410750</v>
       </c>
       <c r="F276" s="37" t="s">
@@ -52630,7 +52614,7 @@
       <c r="D277" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="E277" s="306">
+      <c r="E277" s="304">
         <v>335708848</v>
       </c>
       <c r="F277" s="37" t="s">
@@ -52678,7 +52662,7 @@
       <c r="D278" s="37" t="s">
         <v>429</v>
       </c>
-      <c r="E278" s="306">
+      <c r="E278" s="304">
         <v>334875507</v>
       </c>
       <c r="F278" s="37" t="s">
@@ -52726,7 +52710,7 @@
       <c r="D279" s="37" t="s">
         <v>353</v>
       </c>
-      <c r="E279" s="306">
+      <c r="E279" s="304">
         <v>219079084</v>
       </c>
       <c r="F279" s="37" t="s">
@@ -52774,7 +52758,7 @@
       <c r="D280" s="37" t="s">
         <v>407</v>
       </c>
-      <c r="E280" s="306">
+      <c r="E280" s="304">
         <v>219485547</v>
       </c>
       <c r="F280" s="37" t="s">
@@ -52822,7 +52806,7 @@
       <c r="D281" s="37" t="s">
         <v>238</v>
       </c>
-      <c r="E281" s="306">
+      <c r="E281" s="304">
         <v>219477734</v>
       </c>
       <c r="F281" s="37" t="s">
@@ -52870,7 +52854,7 @@
       <c r="D282" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E282" s="306">
+      <c r="E282" s="304">
         <v>219377173</v>
       </c>
       <c r="F282" s="37" t="s">
@@ -52918,7 +52902,7 @@
       <c r="D283" s="37" t="s">
         <v>429</v>
       </c>
-      <c r="E283" s="306">
+      <c r="E283" s="304">
         <v>220384556</v>
       </c>
       <c r="F283" s="37" t="s">
@@ -52966,7 +52950,7 @@
       <c r="D284" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E284" s="306">
+      <c r="E284" s="304">
         <v>215496639</v>
       </c>
       <c r="F284" s="37" t="s">
@@ -53014,7 +52998,7 @@
       <c r="D285" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="E285" s="306">
+      <c r="E285" s="304">
         <v>336766639</v>
       </c>
       <c r="F285" s="37" t="s">
@@ -53062,7 +53046,7 @@
       <c r="D286" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="E286" s="306">
+      <c r="E286" s="304">
         <v>334417649</v>
       </c>
       <c r="F286" s="37" t="s">
@@ -53110,7 +53094,7 @@
       <c r="D287" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E287" s="306">
+      <c r="E287" s="304">
         <v>335517660</v>
       </c>
       <c r="F287" s="37" t="s">
@@ -53158,7 +53142,7 @@
       <c r="D288" s="37" t="s">
         <v>407</v>
       </c>
-      <c r="E288" s="306">
+      <c r="E288" s="304">
         <v>218888741</v>
       </c>
       <c r="F288" s="37" t="s">
@@ -53206,7 +53190,7 @@
       <c r="D289" s="37" t="s">
         <v>965</v>
       </c>
-      <c r="E289" s="306">
+      <c r="E289" s="304">
         <v>217237171</v>
       </c>
       <c r="F289" s="37" t="s">
@@ -53254,7 +53238,7 @@
       <c r="D290" s="37" t="s">
         <v>429</v>
       </c>
-      <c r="E290" s="306">
+      <c r="E290" s="304">
         <v>334875507</v>
       </c>
       <c r="F290" s="37" t="s">
@@ -53302,7 +53286,7 @@
       <c r="D291" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="E291" s="306">
+      <c r="E291" s="304">
         <v>335165619</v>
       </c>
       <c r="F291" s="37" t="s">
@@ -53350,7 +53334,7 @@
       <c r="D292" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E292" s="306">
+      <c r="E292" s="304">
         <v>334801677</v>
       </c>
       <c r="F292" s="37" t="s">
@@ -53398,7 +53382,7 @@
       <c r="D293" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="E293" s="306">
+      <c r="E293" s="304">
         <v>337039945</v>
       </c>
       <c r="F293" s="37" t="s">
@@ -53446,7 +53430,7 @@
       <c r="D294" s="37" t="s">
         <v>407</v>
       </c>
-      <c r="E294" s="306">
+      <c r="E294" s="304">
         <v>217844539</v>
       </c>
       <c r="F294" s="37" t="s">
@@ -53494,7 +53478,7 @@
       <c r="D295" s="37" t="s">
         <v>965</v>
       </c>
-      <c r="E295" s="306">
+      <c r="E295" s="304">
         <v>218746204</v>
       </c>
       <c r="F295" s="37" t="s">
@@ -53542,7 +53526,7 @@
       <c r="D296" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="E296" s="306">
+      <c r="E296" s="304">
         <v>335145074</v>
       </c>
       <c r="F296" s="37" t="s">
@@ -53590,7 +53574,7 @@
       <c r="D297" s="37" t="s">
         <v>96</v>
       </c>
-      <c r="E297" s="306">
+      <c r="E297" s="304">
         <v>335265443</v>
       </c>
       <c r="F297" s="37" t="s">
@@ -53638,7 +53622,7 @@
       <c r="D298" s="41" t="s">
         <v>429</v>
       </c>
-      <c r="E298" s="311">
+      <c r="E298" s="309">
         <v>335152286</v>
       </c>
       <c r="F298" s="41" t="s">
@@ -53674,48 +53658,48 @@
       </c>
     </row>
     <row r="299" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A299" s="420">
+      <c r="A299" s="414">
         <v>43</v>
       </c>
-      <c r="B299" s="421" t="s">
+      <c r="B299" s="415" t="s">
         <v>32</v>
       </c>
-      <c r="C299" s="421" t="s">
+      <c r="C299" s="415" t="s">
         <v>32</v>
       </c>
-      <c r="D299" s="422" t="s">
+      <c r="D299" s="416" t="s">
         <v>1315</v>
       </c>
-      <c r="E299" s="423">
+      <c r="E299" s="417">
         <v>334926508</v>
       </c>
-      <c r="F299" s="422" t="s">
+      <c r="F299" s="416" t="s">
         <v>344</v>
       </c>
-      <c r="G299" s="422" t="s">
+      <c r="G299" s="416" t="s">
         <v>1313</v>
       </c>
-      <c r="H299" s="422"/>
-      <c r="I299" s="422" t="s">
+      <c r="H299" s="416"/>
+      <c r="I299" s="416" t="s">
         <v>346</v>
       </c>
-      <c r="J299" s="422" t="s">
+      <c r="J299" s="416" t="s">
         <v>1314</v>
       </c>
-      <c r="K299" s="424"/>
-      <c r="L299" s="424" t="s">
+      <c r="K299" s="418"/>
+      <c r="L299" s="418" t="s">
         <v>1316</v>
       </c>
-      <c r="M299" s="425" t="s">
+      <c r="M299" s="419" t="s">
         <v>1304</v>
       </c>
-      <c r="N299" s="428" t="s">
+      <c r="N299" s="422" t="s">
         <v>1317</v>
       </c>
-      <c r="O299" s="425" t="s">
+      <c r="O299" s="419" t="s">
         <v>1305</v>
       </c>
-      <c r="P299" s="426">
+      <c r="P299" s="420">
         <v>0.72916666666666663</v>
       </c>
     </row>
@@ -53732,7 +53716,7 @@
       <c r="D300" s="238" t="s">
         <v>376</v>
       </c>
-      <c r="E300" s="323">
+      <c r="E300" s="321">
         <v>334584802</v>
       </c>
       <c r="F300" s="238" t="s">
@@ -53750,8 +53734,8 @@
       <c r="J300" s="238" t="s">
         <v>987</v>
       </c>
-      <c r="K300" s="346"/>
-      <c r="L300" s="346" t="s">
+      <c r="K300" s="343"/>
+      <c r="L300" s="343" t="s">
         <v>991</v>
       </c>
       <c r="M300" s="239" t="s">
@@ -53768,48 +53752,48 @@
       </c>
     </row>
     <row r="301" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A301" s="405">
+      <c r="A301" s="401">
         <v>2</v>
       </c>
-      <c r="B301" s="406" t="s">
+      <c r="B301" s="402" t="s">
         <v>129</v>
       </c>
-      <c r="C301" s="407" t="s">
+      <c r="C301" s="403" t="s">
         <v>541</v>
       </c>
-      <c r="D301" s="399" t="s">
+      <c r="D301" s="396" t="s">
         <v>353</v>
       </c>
-      <c r="E301" s="400">
+      <c r="E301" s="397">
         <v>219753605</v>
       </c>
-      <c r="F301" s="401" t="s">
+      <c r="F301" s="398" t="s">
         <v>976</v>
       </c>
-      <c r="G301" s="401" t="s">
+      <c r="G301" s="398" t="s">
         <v>972</v>
       </c>
-      <c r="H301" s="402"/>
-      <c r="I301" s="399" t="s">
+      <c r="H301" s="398"/>
+      <c r="I301" s="396" t="s">
         <v>977</v>
       </c>
-      <c r="J301" s="399" t="s">
+      <c r="J301" s="396" t="s">
         <v>974</v>
       </c>
-      <c r="K301" s="403"/>
-      <c r="L301" s="407" t="s">
+      <c r="K301" s="399"/>
+      <c r="L301" s="403" t="s">
         <v>1318</v>
       </c>
-      <c r="M301" s="404" t="s">
+      <c r="M301" s="400" t="s">
         <v>84</v>
       </c>
-      <c r="N301" s="427" t="s">
+      <c r="N301" s="421" t="s">
         <v>1317</v>
       </c>
-      <c r="O301" s="404" t="s">
+      <c r="O301" s="400" t="s">
         <v>1310</v>
       </c>
-      <c r="P301" s="408">
+      <c r="P301" s="404">
         <v>0.72986111111111107</v>
       </c>
     </row>
@@ -53826,7 +53810,7 @@
       <c r="D302" s="244" t="s">
         <v>26</v>
       </c>
-      <c r="E302" s="324">
+      <c r="E302" s="322">
         <v>220342273</v>
       </c>
       <c r="F302" s="244" t="s">
@@ -53844,8 +53828,8 @@
       <c r="J302" s="244" t="s">
         <v>210</v>
       </c>
-      <c r="K302" s="347"/>
-      <c r="L302" s="347" t="s">
+      <c r="K302" s="344"/>
+      <c r="L302" s="344" t="s">
         <v>44</v>
       </c>
       <c r="M302" s="245" t="s">
@@ -53874,7 +53858,7 @@
       <c r="D303" s="244" t="s">
         <v>276</v>
       </c>
-      <c r="E303" s="324">
+      <c r="E303" s="322">
         <v>220611503</v>
       </c>
       <c r="F303" s="244" t="s">
@@ -53892,8 +53876,8 @@
       <c r="J303" s="244" t="s">
         <v>539</v>
       </c>
-      <c r="K303" s="347"/>
-      <c r="L303" s="347" t="s">
+      <c r="K303" s="344"/>
+      <c r="L303" s="344" t="s">
         <v>544</v>
       </c>
       <c r="M303" s="245" t="s">
@@ -53922,7 +53906,7 @@
       <c r="D304" s="244" t="s">
         <v>376</v>
       </c>
-      <c r="E304" s="324">
+      <c r="E304" s="322">
         <v>218956738</v>
       </c>
       <c r="F304" s="244" t="s">
@@ -53940,8 +53924,8 @@
       <c r="J304" s="244" t="s">
         <v>512</v>
       </c>
-      <c r="K304" s="347"/>
-      <c r="L304" s="347" t="s">
+      <c r="K304" s="344"/>
+      <c r="L304" s="344" t="s">
         <v>840</v>
       </c>
       <c r="M304" s="245" t="s">
@@ -53970,7 +53954,7 @@
       <c r="D305" s="244" t="s">
         <v>26</v>
       </c>
-      <c r="E305" s="324">
+      <c r="E305" s="322">
         <v>334880440</v>
       </c>
       <c r="F305" s="244" t="s">
@@ -53988,8 +53972,8 @@
       <c r="J305" s="244" t="s">
         <v>1061</v>
       </c>
-      <c r="K305" s="347"/>
-      <c r="L305" s="347" t="s">
+      <c r="K305" s="344"/>
+      <c r="L305" s="344" t="s">
         <v>1062</v>
       </c>
       <c r="M305" s="245" t="s">
@@ -54018,7 +54002,7 @@
       <c r="D306" s="244" t="s">
         <v>429</v>
       </c>
-      <c r="E306" s="324">
+      <c r="E306" s="322">
         <v>337619654</v>
       </c>
       <c r="F306" s="244" t="s">
@@ -54036,8 +54020,8 @@
       <c r="J306" s="244" t="s">
         <v>1071</v>
       </c>
-      <c r="K306" s="347"/>
-      <c r="L306" s="347" t="s">
+      <c r="K306" s="344"/>
+      <c r="L306" s="344" t="s">
         <v>1072</v>
       </c>
       <c r="M306" s="245" t="s">
@@ -54066,7 +54050,7 @@
       <c r="D307" s="244" t="s">
         <v>131</v>
       </c>
-      <c r="E307" s="324">
+      <c r="E307" s="322">
         <v>218762631</v>
       </c>
       <c r="F307" s="244" t="s">
@@ -54084,8 +54068,8 @@
       <c r="J307" s="244" t="s">
         <v>135</v>
       </c>
-      <c r="K307" s="347"/>
-      <c r="L307" s="347" t="s">
+      <c r="K307" s="344"/>
+      <c r="L307" s="344" t="s">
         <v>136</v>
       </c>
       <c r="M307" s="245" t="s">
@@ -54114,7 +54098,7 @@
       <c r="D308" s="244" t="s">
         <v>73</v>
       </c>
-      <c r="E308" s="324">
+      <c r="E308" s="322">
         <v>334398401</v>
       </c>
       <c r="F308" s="244" t="s">
@@ -54132,8 +54116,8 @@
       <c r="J308" s="244" t="s">
         <v>368</v>
       </c>
-      <c r="K308" s="347"/>
-      <c r="L308" s="347" t="s">
+      <c r="K308" s="344"/>
+      <c r="L308" s="344" t="s">
         <v>369</v>
       </c>
       <c r="M308" s="245" t="s">
@@ -54162,7 +54146,7 @@
       <c r="D309" s="250" t="s">
         <v>59</v>
       </c>
-      <c r="E309" s="325">
+      <c r="E309" s="323">
         <v>334844545</v>
       </c>
       <c r="F309" s="250" t="s">
@@ -54180,8 +54164,8 @@
       <c r="J309" s="250" t="s">
         <v>1185</v>
       </c>
-      <c r="K309" s="348"/>
-      <c r="L309" s="348" t="s">
+      <c r="K309" s="345"/>
+      <c r="L309" s="345" t="s">
         <v>1186</v>
       </c>
       <c r="M309" s="251" t="s">
@@ -54197,53 +54181,53 @@
         <v>0.72986111111111107</v>
       </c>
     </row>
-    <row r="310" spans="1:16" ht="34.799999999999997" x14ac:dyDescent="0.3">
-      <c r="A310" s="393" t="s">
+    <row r="310" spans="1:16" ht="36" x14ac:dyDescent="0.35">
+      <c r="A310" s="390" t="s">
         <v>1284</v>
       </c>
-      <c r="B310" s="394" t="s">
+      <c r="B310" s="391" t="s">
         <v>1290</v>
       </c>
-      <c r="C310" s="394" t="s">
+      <c r="C310" s="391" t="s">
         <v>0</v>
       </c>
-      <c r="D310" s="395" t="s">
+      <c r="D310" s="392" t="s">
         <v>1</v>
       </c>
-      <c r="E310" s="394" t="s">
+      <c r="E310" s="391" t="s">
         <v>1291</v>
       </c>
-      <c r="F310" s="395" t="s">
+      <c r="F310" s="392" t="s">
         <v>2</v>
       </c>
-      <c r="G310" s="395" t="s">
+      <c r="G310" s="392" t="s">
         <v>3</v>
       </c>
-      <c r="H310" s="395" t="s">
+      <c r="H310" s="392" t="s">
         <v>4</v>
       </c>
-      <c r="I310" s="395" t="s">
+      <c r="I310" s="392" t="s">
         <v>1292</v>
       </c>
-      <c r="J310" s="395" t="s">
+      <c r="J310" s="392" t="s">
         <v>1293</v>
       </c>
-      <c r="K310" s="396" t="s">
+      <c r="K310" s="393" t="s">
         <v>1294</v>
       </c>
-      <c r="L310" s="394" t="s">
+      <c r="L310" s="391" t="s">
         <v>6</v>
       </c>
-      <c r="M310" s="394" t="s">
+      <c r="M310" s="391" t="s">
         <v>5</v>
       </c>
-      <c r="N310" s="397" t="s">
+      <c r="N310" s="394" t="s">
         <v>1285</v>
       </c>
-      <c r="O310" s="394" t="s">
+      <c r="O310" s="391" t="s">
         <v>1286</v>
       </c>
-      <c r="P310" s="398" t="s">
+      <c r="P310" s="395" t="s">
         <v>1287</v>
       </c>
     </row>
@@ -54260,7 +54244,7 @@
       <c r="D311" s="30" t="s">
         <v>227</v>
       </c>
-      <c r="E311" s="295">
+      <c r="E311" s="293">
         <v>220652002</v>
       </c>
       <c r="F311" s="30" t="s">
@@ -54278,8 +54262,8 @@
       <c r="J311" s="30" t="s">
         <v>620</v>
       </c>
-      <c r="K311" s="349"/>
-      <c r="L311" s="349" t="s">
+      <c r="K311" s="346"/>
+      <c r="L311" s="346" t="s">
         <v>622</v>
       </c>
       <c r="M311" s="31" t="s">
@@ -54308,7 +54292,7 @@
       <c r="D312" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E312" s="296">
+      <c r="E312" s="294">
         <v>335319240</v>
       </c>
       <c r="F312" s="26" t="s">
@@ -54356,7 +54340,7 @@
       <c r="D313" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="E313" s="296">
+      <c r="E313" s="294">
         <v>220585392</v>
       </c>
       <c r="F313" s="26" t="s">
@@ -54404,7 +54388,7 @@
       <c r="D314" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="E314" s="296">
+      <c r="E314" s="294">
         <v>337019129</v>
       </c>
       <c r="F314" s="26" t="s">
@@ -54452,7 +54436,7 @@
       <c r="D315" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="E315" s="296">
+      <c r="E315" s="294">
         <v>220908453</v>
       </c>
       <c r="F315" s="26" t="s">
@@ -54500,7 +54484,7 @@
       <c r="D316" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="E316" s="296">
+      <c r="E316" s="294">
         <v>336580873</v>
       </c>
       <c r="F316" s="26" t="s">
@@ -54548,7 +54532,7 @@
       <c r="D317" s="26" t="s">
         <v>965</v>
       </c>
-      <c r="E317" s="296">
+      <c r="E317" s="294">
         <v>319135414</v>
       </c>
       <c r="F317" s="26" t="s">
@@ -54596,7 +54580,7 @@
       <c r="D318" s="26" t="s">
         <v>1077</v>
       </c>
-      <c r="E318" s="296">
+      <c r="E318" s="294">
         <v>220962807</v>
       </c>
       <c r="F318" s="26" t="s">
@@ -54644,7 +54628,7 @@
       <c r="D319" s="26" t="s">
         <v>1077</v>
       </c>
-      <c r="E319" s="296">
+      <c r="E319" s="294">
         <v>220907398</v>
       </c>
       <c r="F319" s="26" t="s">
@@ -54692,7 +54676,7 @@
       <c r="D320" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="E320" s="296">
+      <c r="E320" s="294">
         <v>337122956</v>
       </c>
       <c r="F320" s="26" t="s">
@@ -54740,7 +54724,7 @@
       <c r="D321" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="E321" s="296">
+      <c r="E321" s="294">
         <v>221015134</v>
       </c>
       <c r="F321" s="26" t="s">
@@ -54776,350 +54760,350 @@
       </c>
     </row>
     <row r="322" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A322" s="377">
+      <c r="A322" s="374">
         <v>12</v>
       </c>
-      <c r="B322" s="378" t="s">
+      <c r="B322" s="375" t="s">
         <v>72</v>
       </c>
-      <c r="C322" s="378" t="s">
+      <c r="C322" s="375" t="s">
         <v>72</v>
       </c>
-      <c r="D322" s="379" t="s">
+      <c r="D322" s="376" t="s">
         <v>19</v>
       </c>
-      <c r="E322" s="380">
+      <c r="E322" s="377">
         <v>220671226</v>
       </c>
-      <c r="F322" s="379" t="s">
+      <c r="F322" s="376" t="s">
         <v>398</v>
       </c>
-      <c r="G322" s="379" t="s">
+      <c r="G322" s="376" t="s">
         <v>21</v>
       </c>
-      <c r="H322" s="379" t="s">
+      <c r="H322" s="376" t="s">
         <v>399</v>
       </c>
-      <c r="I322" s="379" t="s">
+      <c r="I322" s="376" t="s">
         <v>400</v>
       </c>
-      <c r="J322" s="379" t="s">
+      <c r="J322" s="376" t="s">
         <v>401</v>
       </c>
-      <c r="K322" s="381"/>
-      <c r="L322" s="381" t="s">
+      <c r="K322" s="378"/>
+      <c r="L322" s="378" t="s">
         <v>402</v>
       </c>
-      <c r="M322" s="382" t="s">
+      <c r="M322" s="379" t="s">
         <v>15</v>
       </c>
-      <c r="N322" s="383">
+      <c r="N322" s="380">
         <v>912</v>
       </c>
-      <c r="O322" s="381" t="s">
+      <c r="O322" s="378" t="s">
         <v>1288</v>
       </c>
-      <c r="P322" s="384">
+      <c r="P322" s="381">
         <v>0.75</v>
       </c>
     </row>
     <row r="323" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A323" s="385">
+      <c r="A323" s="382">
         <v>1</v>
       </c>
-      <c r="B323" s="386" t="s">
+      <c r="B323" s="383" t="s">
         <v>137</v>
       </c>
-      <c r="C323" s="386" t="s">
+      <c r="C323" s="383" t="s">
         <v>137</v>
       </c>
-      <c r="D323" s="387" t="s">
+      <c r="D323" s="384" t="s">
         <v>227</v>
       </c>
-      <c r="E323" s="388">
+      <c r="E323" s="385">
         <v>220648430</v>
       </c>
-      <c r="F323" s="387" t="s">
+      <c r="F323" s="384" t="s">
         <v>91</v>
       </c>
-      <c r="G323" s="387" t="s">
+      <c r="G323" s="384" t="s">
         <v>307</v>
       </c>
-      <c r="H323" s="387" t="s">
+      <c r="H323" s="384" t="s">
         <v>12</v>
       </c>
-      <c r="I323" s="387" t="s">
+      <c r="I323" s="384" t="s">
         <v>93</v>
       </c>
-      <c r="J323" s="387" t="s">
+      <c r="J323" s="384" t="s">
         <v>308</v>
       </c>
-      <c r="K323" s="389"/>
-      <c r="L323" s="389" t="s">
+      <c r="K323" s="386"/>
+      <c r="L323" s="386" t="s">
         <v>309</v>
       </c>
-      <c r="M323" s="390" t="s">
+      <c r="M323" s="387" t="s">
         <v>15</v>
       </c>
-      <c r="N323" s="391">
+      <c r="N323" s="388">
         <v>913</v>
       </c>
-      <c r="O323" s="390" t="s">
+      <c r="O323" s="387" t="s">
         <v>1305</v>
       </c>
-      <c r="P323" s="392">
+      <c r="P323" s="389">
         <v>0.75</v>
       </c>
     </row>
     <row r="324" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A324" s="361">
+      <c r="A324" s="358">
         <v>2</v>
       </c>
-      <c r="B324" s="362" t="s">
+      <c r="B324" s="359" t="s">
         <v>137</v>
       </c>
-      <c r="C324" s="362" t="s">
+      <c r="C324" s="359" t="s">
         <v>137</v>
       </c>
-      <c r="D324" s="363" t="s">
+      <c r="D324" s="360" t="s">
         <v>102</v>
       </c>
-      <c r="E324" s="364">
+      <c r="E324" s="361">
         <v>221711252</v>
       </c>
-      <c r="F324" s="363" t="s">
+      <c r="F324" s="360" t="s">
         <v>138</v>
       </c>
-      <c r="G324" s="363" t="s">
+      <c r="G324" s="360" t="s">
         <v>139</v>
       </c>
-      <c r="H324" s="363" t="s">
+      <c r="H324" s="360" t="s">
         <v>12</v>
       </c>
-      <c r="I324" s="363" t="s">
+      <c r="I324" s="360" t="s">
         <v>140</v>
       </c>
-      <c r="J324" s="363" t="s">
+      <c r="J324" s="360" t="s">
         <v>141</v>
       </c>
-      <c r="K324" s="365"/>
-      <c r="L324" s="365" t="s">
+      <c r="K324" s="362"/>
+      <c r="L324" s="362" t="s">
         <v>142</v>
       </c>
-      <c r="M324" s="366" t="s">
+      <c r="M324" s="363" t="s">
         <v>15</v>
       </c>
-      <c r="N324" s="367">
+      <c r="N324" s="364">
         <v>914</v>
       </c>
-      <c r="O324" s="366" t="s">
+      <c r="O324" s="363" t="s">
         <v>1305</v>
       </c>
-      <c r="P324" s="368">
+      <c r="P324" s="365">
         <v>0.75</v>
       </c>
     </row>
     <row r="325" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A325" s="361">
+      <c r="A325" s="358">
         <v>3</v>
       </c>
-      <c r="B325" s="362" t="s">
+      <c r="B325" s="359" t="s">
         <v>137</v>
       </c>
-      <c r="C325" s="362" t="s">
+      <c r="C325" s="359" t="s">
         <v>137</v>
       </c>
-      <c r="D325" s="363" t="s">
+      <c r="D325" s="360" t="s">
         <v>73</v>
       </c>
-      <c r="E325" s="364">
+      <c r="E325" s="361">
         <v>338179633</v>
       </c>
-      <c r="F325" s="363" t="s">
+      <c r="F325" s="360" t="s">
         <v>603</v>
       </c>
-      <c r="G325" s="363" t="s">
+      <c r="G325" s="360" t="s">
         <v>604</v>
       </c>
-      <c r="H325" s="363" t="s">
+      <c r="H325" s="360" t="s">
         <v>12</v>
       </c>
-      <c r="I325" s="363" t="s">
+      <c r="I325" s="360" t="s">
         <v>605</v>
       </c>
-      <c r="J325" s="363" t="s">
+      <c r="J325" s="360" t="s">
         <v>606</v>
       </c>
-      <c r="K325" s="365"/>
-      <c r="L325" s="365" t="s">
+      <c r="K325" s="362"/>
+      <c r="L325" s="362" t="s">
         <v>607</v>
       </c>
-      <c r="M325" s="366" t="s">
+      <c r="M325" s="363" t="s">
         <v>15</v>
       </c>
-      <c r="N325" s="367">
+      <c r="N325" s="364">
         <v>915</v>
       </c>
-      <c r="O325" s="366" t="s">
+      <c r="O325" s="363" t="s">
         <v>1305</v>
       </c>
-      <c r="P325" s="368">
+      <c r="P325" s="365">
         <v>0.75</v>
       </c>
     </row>
     <row r="326" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A326" s="361">
+      <c r="A326" s="358">
         <v>4</v>
       </c>
-      <c r="B326" s="362" t="s">
+      <c r="B326" s="359" t="s">
         <v>137</v>
       </c>
-      <c r="C326" s="362" t="s">
+      <c r="C326" s="359" t="s">
         <v>137</v>
       </c>
-      <c r="D326" s="363" t="s">
+      <c r="D326" s="360" t="s">
         <v>353</v>
       </c>
-      <c r="E326" s="364">
+      <c r="E326" s="361">
         <v>337196679</v>
       </c>
-      <c r="F326" s="363" t="s">
+      <c r="F326" s="360" t="s">
         <v>442</v>
       </c>
-      <c r="G326" s="363" t="s">
+      <c r="G326" s="360" t="s">
         <v>926</v>
       </c>
-      <c r="H326" s="363" t="s">
+      <c r="H326" s="360" t="s">
         <v>12</v>
       </c>
-      <c r="I326" s="363" t="s">
+      <c r="I326" s="360" t="s">
         <v>223</v>
       </c>
-      <c r="J326" s="363" t="s">
+      <c r="J326" s="360" t="s">
         <v>927</v>
       </c>
-      <c r="K326" s="365"/>
-      <c r="L326" s="365" t="s">
+      <c r="K326" s="362"/>
+      <c r="L326" s="362" t="s">
         <v>928</v>
       </c>
-      <c r="M326" s="366" t="s">
+      <c r="M326" s="363" t="s">
         <v>15</v>
       </c>
-      <c r="N326" s="367">
+      <c r="N326" s="364">
         <v>916</v>
       </c>
-      <c r="O326" s="366" t="s">
+      <c r="O326" s="363" t="s">
         <v>1305</v>
       </c>
-      <c r="P326" s="368">
+      <c r="P326" s="365">
         <v>0.75</v>
       </c>
     </row>
     <row r="327" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A327" s="361">
+      <c r="A327" s="358">
         <v>5</v>
       </c>
-      <c r="B327" s="362" t="s">
+      <c r="B327" s="359" t="s">
         <v>137</v>
       </c>
-      <c r="C327" s="362" t="s">
+      <c r="C327" s="359" t="s">
         <v>137</v>
       </c>
-      <c r="D327" s="363" t="s">
+      <c r="D327" s="360" t="s">
         <v>429</v>
       </c>
-      <c r="E327" s="364">
+      <c r="E327" s="361">
         <v>221711211</v>
       </c>
-      <c r="F327" s="363" t="s">
+      <c r="F327" s="360" t="s">
         <v>698</v>
       </c>
-      <c r="G327" s="363" t="s">
+      <c r="G327" s="360" t="s">
         <v>1195</v>
       </c>
-      <c r="H327" s="363" t="s">
+      <c r="H327" s="360" t="s">
         <v>12</v>
       </c>
-      <c r="I327" s="363" t="s">
+      <c r="I327" s="360" t="s">
         <v>700</v>
       </c>
-      <c r="J327" s="363" t="s">
+      <c r="J327" s="360" t="s">
         <v>1196</v>
       </c>
-      <c r="K327" s="365"/>
-      <c r="L327" s="365" t="s">
+      <c r="K327" s="362"/>
+      <c r="L327" s="362" t="s">
         <v>142</v>
       </c>
-      <c r="M327" s="366" t="s">
+      <c r="M327" s="363" t="s">
         <v>15</v>
       </c>
-      <c r="N327" s="367">
+      <c r="N327" s="364">
         <v>917</v>
       </c>
-      <c r="O327" s="366" t="s">
+      <c r="O327" s="363" t="s">
         <v>1305</v>
       </c>
-      <c r="P327" s="368">
+      <c r="P327" s="365">
         <v>0.75</v>
       </c>
     </row>
     <row r="328" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A328" s="369">
+      <c r="A328" s="366">
         <v>6</v>
       </c>
-      <c r="B328" s="370" t="s">
+      <c r="B328" s="367" t="s">
         <v>137</v>
       </c>
-      <c r="C328" s="370" t="s">
+      <c r="C328" s="367" t="s">
         <v>137</v>
       </c>
-      <c r="D328" s="371" t="s">
+      <c r="D328" s="368" t="s">
         <v>26</v>
       </c>
-      <c r="E328" s="372">
+      <c r="E328" s="369">
         <v>221674716</v>
       </c>
-      <c r="F328" s="371" t="s">
+      <c r="F328" s="368" t="s">
         <v>247</v>
       </c>
-      <c r="G328" s="371" t="s">
+      <c r="G328" s="368" t="s">
         <v>426</v>
       </c>
-      <c r="H328" s="371" t="s">
+      <c r="H328" s="368" t="s">
         <v>12</v>
       </c>
-      <c r="I328" s="371" t="s">
+      <c r="I328" s="368" t="s">
         <v>249</v>
       </c>
-      <c r="J328" s="371" t="s">
+      <c r="J328" s="368" t="s">
         <v>427</v>
       </c>
-      <c r="K328" s="373"/>
-      <c r="L328" s="373" t="s">
+      <c r="K328" s="370"/>
+      <c r="L328" s="370" t="s">
         <v>428</v>
       </c>
-      <c r="M328" s="374" t="s">
+      <c r="M328" s="371" t="s">
         <v>15</v>
       </c>
-      <c r="N328" s="375">
+      <c r="N328" s="372">
         <v>918</v>
       </c>
-      <c r="O328" s="374" t="s">
+      <c r="O328" s="371" t="s">
         <v>1305</v>
       </c>
-      <c r="P328" s="376">
+      <c r="P328" s="373">
         <v>0.75</v>
       </c>
     </row>
     <row r="329" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="K329" s="350"/>
+      <c r="K329" s="347"/>
     </row>
     <row r="330" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A330" s="199" t="s">
         <v>1303</v>
       </c>
       <c r="B330" s="15"/>
-      <c r="K330" s="350"/>
+      <c r="K330" s="347"/>
     </row>
     <row r="331" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A331" s="182" t="s">
@@ -55128,7 +55112,7 @@
       <c r="B331" s="11" t="s">
         <v>1297</v>
       </c>
-      <c r="K331" s="350"/>
+      <c r="K331" s="347"/>
     </row>
     <row r="332" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A332" s="166" t="s">
@@ -55137,7 +55121,7 @@
       <c r="B332" s="12" t="s">
         <v>1298</v>
       </c>
-      <c r="K332" s="350"/>
+      <c r="K332" s="347"/>
     </row>
     <row r="333" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A333" s="167" t="s">
@@ -55146,7 +55130,7 @@
       <c r="B333" s="13" t="s">
         <v>1300</v>
       </c>
-      <c r="K333" s="350"/>
+      <c r="K333" s="347"/>
     </row>
     <row r="334" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A334" s="169" t="s">
@@ -55155,268 +55139,268 @@
       <c r="B334" s="14" t="s">
         <v>1302</v>
       </c>
-      <c r="K334" s="350"/>
+      <c r="K334" s="347"/>
     </row>
     <row r="335" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="K335" s="350"/>
+      <c r="K335" s="347"/>
     </row>
     <row r="336" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="K336" s="350"/>
+      <c r="K336" s="347"/>
     </row>
     <row r="337" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K337" s="350"/>
+      <c r="K337" s="347"/>
     </row>
     <row r="338" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K338" s="350"/>
+      <c r="K338" s="347"/>
     </row>
     <row r="339" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K339" s="350"/>
+      <c r="K339" s="347"/>
     </row>
     <row r="340" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K340" s="350"/>
+      <c r="K340" s="347"/>
     </row>
     <row r="341" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K341" s="350"/>
+      <c r="K341" s="347"/>
     </row>
     <row r="342" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K342" s="350"/>
+      <c r="K342" s="347"/>
     </row>
     <row r="343" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K343" s="350"/>
+      <c r="K343" s="347"/>
     </row>
     <row r="344" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K344" s="350"/>
+      <c r="K344" s="347"/>
     </row>
     <row r="345" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K345" s="350"/>
+      <c r="K345" s="347"/>
     </row>
     <row r="346" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K346" s="350"/>
+      <c r="K346" s="347"/>
     </row>
     <row r="347" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K347" s="350"/>
+      <c r="K347" s="347"/>
     </row>
     <row r="348" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K348" s="350"/>
+      <c r="K348" s="347"/>
     </row>
     <row r="349" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K349" s="350"/>
+      <c r="K349" s="347"/>
     </row>
     <row r="350" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K350" s="350"/>
+      <c r="K350" s="347"/>
     </row>
     <row r="351" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K351" s="350"/>
+      <c r="K351" s="347"/>
     </row>
     <row r="352" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K352" s="350"/>
+      <c r="K352" s="347"/>
     </row>
     <row r="353" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K353" s="350"/>
+      <c r="K353" s="347"/>
     </row>
     <row r="354" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K354" s="350"/>
+      <c r="K354" s="347"/>
     </row>
     <row r="355" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K355" s="350"/>
+      <c r="K355" s="347"/>
     </row>
     <row r="356" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K356" s="350"/>
+      <c r="K356" s="347"/>
     </row>
     <row r="357" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K357" s="350"/>
+      <c r="K357" s="347"/>
     </row>
     <row r="358" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K358" s="350"/>
+      <c r="K358" s="347"/>
     </row>
     <row r="359" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K359" s="350"/>
+      <c r="K359" s="347"/>
     </row>
     <row r="360" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K360" s="350"/>
+      <c r="K360" s="347"/>
     </row>
     <row r="361" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K361" s="350"/>
+      <c r="K361" s="347"/>
     </row>
     <row r="362" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K362" s="350"/>
+      <c r="K362" s="347"/>
     </row>
     <row r="363" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K363" s="350"/>
+      <c r="K363" s="347"/>
     </row>
     <row r="364" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K364" s="350"/>
+      <c r="K364" s="347"/>
     </row>
     <row r="365" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K365" s="350"/>
+      <c r="K365" s="347"/>
     </row>
     <row r="366" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K366" s="350"/>
+      <c r="K366" s="347"/>
     </row>
     <row r="367" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K367" s="350"/>
+      <c r="K367" s="347"/>
     </row>
     <row r="368" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K368" s="350"/>
+      <c r="K368" s="347"/>
     </row>
     <row r="369" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K369" s="350"/>
+      <c r="K369" s="347"/>
     </row>
     <row r="370" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K370" s="350"/>
+      <c r="K370" s="347"/>
     </row>
     <row r="371" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K371" s="350"/>
+      <c r="K371" s="347"/>
     </row>
     <row r="372" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K372" s="350"/>
+      <c r="K372" s="347"/>
     </row>
     <row r="373" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K373" s="350"/>
+      <c r="K373" s="347"/>
     </row>
     <row r="374" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K374" s="350"/>
+      <c r="K374" s="347"/>
     </row>
     <row r="375" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K375" s="350"/>
+      <c r="K375" s="347"/>
     </row>
     <row r="376" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K376" s="350"/>
+      <c r="K376" s="347"/>
     </row>
     <row r="377" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K377" s="350"/>
+      <c r="K377" s="347"/>
     </row>
     <row r="378" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K378" s="350"/>
+      <c r="K378" s="347"/>
     </row>
     <row r="379" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K379" s="350"/>
+      <c r="K379" s="347"/>
     </row>
     <row r="380" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K380" s="350"/>
+      <c r="K380" s="347"/>
     </row>
     <row r="381" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K381" s="350"/>
+      <c r="K381" s="347"/>
     </row>
     <row r="382" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K382" s="350"/>
+      <c r="K382" s="347"/>
     </row>
     <row r="383" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K383" s="350"/>
+      <c r="K383" s="347"/>
     </row>
     <row r="384" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K384" s="350"/>
+      <c r="K384" s="347"/>
     </row>
     <row r="385" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K385" s="350"/>
+      <c r="K385" s="347"/>
     </row>
     <row r="386" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K386" s="350"/>
+      <c r="K386" s="347"/>
     </row>
     <row r="387" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K387" s="350"/>
+      <c r="K387" s="347"/>
     </row>
     <row r="388" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K388" s="350"/>
+      <c r="K388" s="347"/>
     </row>
     <row r="389" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K389" s="350"/>
+      <c r="K389" s="347"/>
     </row>
     <row r="390" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K390" s="350"/>
+      <c r="K390" s="347"/>
     </row>
     <row r="391" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K391" s="350"/>
+      <c r="K391" s="347"/>
     </row>
     <row r="392" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K392" s="350"/>
+      <c r="K392" s="347"/>
     </row>
     <row r="393" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K393" s="350"/>
+      <c r="K393" s="347"/>
     </row>
     <row r="394" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K394" s="350"/>
+      <c r="K394" s="347"/>
     </row>
     <row r="395" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K395" s="350"/>
+      <c r="K395" s="347"/>
     </row>
     <row r="396" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K396" s="350"/>
+      <c r="K396" s="347"/>
     </row>
     <row r="397" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K397" s="350"/>
+      <c r="K397" s="347"/>
     </row>
     <row r="398" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K398" s="350"/>
+      <c r="K398" s="347"/>
     </row>
     <row r="399" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K399" s="350"/>
+      <c r="K399" s="347"/>
     </row>
     <row r="400" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K400" s="350"/>
+      <c r="K400" s="347"/>
     </row>
     <row r="401" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K401" s="350"/>
+      <c r="K401" s="347"/>
     </row>
     <row r="402" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K402" s="350"/>
+      <c r="K402" s="347"/>
     </row>
     <row r="403" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K403" s="350"/>
+      <c r="K403" s="347"/>
     </row>
     <row r="404" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K404" s="350"/>
+      <c r="K404" s="347"/>
     </row>
     <row r="405" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K405" s="350"/>
+      <c r="K405" s="347"/>
     </row>
     <row r="406" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K406" s="350"/>
+      <c r="K406" s="347"/>
     </row>
     <row r="407" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K407" s="350"/>
+      <c r="K407" s="347"/>
     </row>
     <row r="408" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K408" s="350"/>
+      <c r="K408" s="347"/>
     </row>
     <row r="409" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K409" s="350"/>
+      <c r="K409" s="347"/>
     </row>
     <row r="410" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K410" s="350"/>
+      <c r="K410" s="347"/>
     </row>
     <row r="411" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K411" s="350"/>
+      <c r="K411" s="347"/>
     </row>
     <row r="412" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K412" s="350"/>
+      <c r="K412" s="347"/>
     </row>
     <row r="413" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K413" s="350"/>
+      <c r="K413" s="347"/>
     </row>
     <row r="414" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K414" s="350"/>
+      <c r="K414" s="347"/>
     </row>
     <row r="415" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K415" s="350"/>
+      <c r="K415" s="347"/>
     </row>
     <row r="416" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K416" s="350"/>
+      <c r="K416" s="347"/>
     </row>
     <row r="417" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K417" s="350"/>
+      <c r="K417" s="347"/>
     </row>
     <row r="418" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K418" s="350"/>
+      <c r="K418" s="347"/>
     </row>
     <row r="419" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K419" s="350"/>
+      <c r="K419" s="347"/>
     </row>
     <row r="420" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K420" s="350"/>
+      <c r="K420" s="347"/>
     </row>
     <row r="421" spans="11:11" x14ac:dyDescent="0.3">
-      <c r="K421" s="350"/>
+      <c r="K421" s="347"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:P26">
